--- a/data/processed/sam_auto_dashboard_2024_refresh/occ_change_by_education/segment_occ_change_by_education_2024_2030.xlsx
+++ b/data/processed/sam_auto_dashboard_2024_refresh/occ_change_by_education/segment_occ_change_by_education_2024_2030.xlsx
@@ -1,23 +1,17 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29426"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vasilauskas\GitHub\EV-Transition\data\processed\sam_auto_dashboard_2024_refresh\occ_change_by_education\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6631EB53-8C01-439C-A1A3-9116A5939331}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
     <sheet name="Education" sheetId="1" r:id="rId1"/>
     <sheet name="Education+Training" sheetId="2" r:id="rId2"/>
     <sheet name="Edu+Training (custom)" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -120,13 +114,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
-    <numFmt numFmtId="43" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="165" formatCode="_(* #,##0_);_(* \(#,##0\);_(* &quot;-&quot;??_);_(@_)"/>
-    <numFmt numFmtId="166" formatCode="0.0%"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <fonts count="2">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -136,13 +125,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -182,47 +164,27 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="1" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
-    <a:clrScheme name="Office 2007 - 2010">
+    <a:clrScheme name="Office">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -260,7 +222,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office 2007 - 2010">
+    <a:fontScheme name="Office">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -294,7 +256,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -329,10 +290,9 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office 2007 - 2010">
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -505,11 +465,11 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -541,7 +501,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -564,16 +524,16 @@
         <v>3451.96904055808</v>
       </c>
       <c r="H2">
-        <v>3302.0626055758371</v>
+        <v>3302.062605575837</v>
       </c>
       <c r="I2">
-        <v>-149.90643498224381</v>
+        <v>-149.9064349822438</v>
       </c>
       <c r="J2">
-        <v>-4.3426355572994478E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.04342635557299448</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -593,19 +553,19 @@
         <v>24</v>
       </c>
       <c r="G3">
-        <v>16795.043196471819</v>
+        <v>16795.04319647182</v>
       </c>
       <c r="H3">
-        <v>15430.953722874239</v>
+        <v>15430.95372287424</v>
       </c>
       <c r="I3">
         <v>-1364.089473597583</v>
       </c>
       <c r="J3">
-        <v>-8.1219765715407108E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.08121976571540711</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -628,16 +588,16 @@
         <v>1000.656548635188</v>
       </c>
       <c r="H4">
-        <v>919.45996493264306</v>
+        <v>919.4599649326431</v>
       </c>
       <c r="I4">
-        <v>-81.196583702544444</v>
+        <v>-81.19658370254444</v>
       </c>
       <c r="J4">
-        <v>-8.1143309173651881E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.08114330917365188</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -660,16 +620,16 @@
         <v>1664.428681321303</v>
       </c>
       <c r="H5">
-        <v>1677.0264075332759</v>
+        <v>1677.026407533276</v>
       </c>
       <c r="I5">
         <v>12.5977262119734</v>
       </c>
       <c r="J5">
-        <v>7.5687990439895101E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.00756879904398951</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -689,19 +649,19 @@
         <v>24</v>
       </c>
       <c r="G6">
-        <v>3887.6393065706889</v>
+        <v>3887.639306570689</v>
       </c>
       <c r="H6">
-        <v>3774.3733987137339</v>
+        <v>3774.373398713734</v>
       </c>
       <c r="I6">
-        <v>-113.26590785695539</v>
+        <v>-113.2659078569554</v>
       </c>
       <c r="J6">
-        <v>-2.9134880817137328E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.02913488081713733</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -721,19 +681,19 @@
         <v>25</v>
       </c>
       <c r="G7">
-        <v>692.51885467863383</v>
+        <v>692.5188546786338</v>
       </c>
       <c r="H7">
-        <v>656.06663913801765</v>
+        <v>656.0666391380176</v>
       </c>
       <c r="I7">
         <v>-36.45221554061618</v>
       </c>
       <c r="J7">
-        <v>-5.2637145247882072E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.05263714524788207</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -753,19 +713,19 @@
         <v>23</v>
       </c>
       <c r="G8">
-        <v>1144.8958530887819</v>
+        <v>1144.895853088782</v>
       </c>
       <c r="H8">
-        <v>992.23011623224909</v>
+        <v>992.2301162322491</v>
       </c>
       <c r="I8">
-        <v>-152.66573685653259</v>
+        <v>-152.6657368565326</v>
       </c>
       <c r="J8">
-        <v>-0.13334465003490059</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.1333446500349006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -785,19 +745,19 @@
         <v>24</v>
       </c>
       <c r="G9">
-        <v>7470.1620513416883</v>
+        <v>7470.162051341688</v>
       </c>
       <c r="H9">
-        <v>6145.3802917563153</v>
+        <v>6145.380291756315</v>
       </c>
       <c r="I9">
         <v>-1324.781759585373</v>
       </c>
       <c r="J9">
-        <v>-0.17734310855377411</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.1773431085537741</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -817,19 +777,19 @@
         <v>25</v>
       </c>
       <c r="G10">
-        <v>408.08169020986338</v>
+        <v>408.0816902098634</v>
       </c>
       <c r="H10">
         <v>332.0668703905082</v>
       </c>
       <c r="I10">
-        <v>-76.014819819355239</v>
+        <v>-76.01481981935524</v>
       </c>
       <c r="J10">
-        <v>-0.18627353699761251</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.1862735369976125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -852,16 +812,16 @@
         <v>2548.713461124355</v>
       </c>
       <c r="H11">
-        <v>2543.0445734705431</v>
+        <v>2543.044573470543</v>
       </c>
       <c r="I11">
-        <v>-5.6688876538119084</v>
+        <v>-5.668887653811908</v>
       </c>
       <c r="J11">
-        <v>-2.2242153699424099E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.00222421536994241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -887,13 +847,13 @@
         <v>10915.53795803819</v>
       </c>
       <c r="I12">
-        <v>-685.30310791949523</v>
+        <v>-685.3031079194952</v>
       </c>
       <c r="J12">
-        <v>-5.9073570961203553E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.05907357096120355</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -913,19 +873,19 @@
         <v>25</v>
       </c>
       <c r="G13">
-        <v>786.88996756620202</v>
+        <v>786.889967566202</v>
       </c>
       <c r="H13">
-        <v>750.45332198619417</v>
+        <v>750.4533219861942</v>
       </c>
       <c r="I13">
-        <v>-36.436645580007848</v>
+        <v>-36.43664558000785</v>
       </c>
       <c r="J13">
-        <v>-4.6304625909393597E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.0463046259093936</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -945,19 +905,19 @@
         <v>23</v>
       </c>
       <c r="G14">
-        <v>2443.9877546628109</v>
+        <v>2443.987754662811</v>
       </c>
       <c r="H14">
         <v>2409.001642550224</v>
       </c>
       <c r="I14">
-        <v>-34.986112112586852</v>
+        <v>-34.98611211258685</v>
       </c>
       <c r="J14">
-        <v>-1.431517488000416E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.01431517488000416</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -977,19 +937,19 @@
         <v>24</v>
       </c>
       <c r="G15">
-        <v>3200.2827458160918</v>
+        <v>3200.282745816092</v>
       </c>
       <c r="H15">
         <v>3140.045112583321</v>
       </c>
       <c r="I15">
-        <v>-60.237633232771259</v>
+        <v>-60.23763323277126</v>
       </c>
       <c r="J15">
-        <v>-1.8822597256921529E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.01882259725692153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -1009,19 +969,19 @@
         <v>25</v>
       </c>
       <c r="G16">
-        <v>342.75438022710011</v>
+        <v>342.7543802271001</v>
       </c>
       <c r="H16">
-        <v>319.64380796077808</v>
+        <v>319.6438079607781</v>
       </c>
       <c r="I16">
-        <v>-23.110572266322041</v>
+        <v>-23.11057226632204</v>
       </c>
       <c r="J16">
-        <v>-6.7426045003449925E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.06742604500344992</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -1041,19 +1001,19 @@
         <v>23</v>
       </c>
       <c r="G17">
-        <v>737.92757910296018</v>
+        <v>737.9275791029602</v>
       </c>
       <c r="H17">
-        <v>756.58045553667444</v>
+        <v>756.5804555366744</v>
       </c>
       <c r="I17">
-        <v>18.652876433714251</v>
+        <v>18.65287643371425</v>
       </c>
       <c r="J17">
-        <v>2.527738081884549E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.02527738081884549</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -1073,19 +1033,19 @@
         <v>24</v>
       </c>
       <c r="G18">
-        <v>199.94970190417479</v>
+        <v>199.9497019041748</v>
       </c>
       <c r="H18">
-        <v>197.24979729783479</v>
+        <v>197.2497972978348</v>
       </c>
       <c r="I18">
-        <v>-2.6999046063399992</v>
+        <v>-2.699904606339999</v>
       </c>
       <c r="J18">
-        <v>-1.3502918887240549E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.01350291888724055</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -1108,16 +1068,16 @@
         <v>94.14822441861125</v>
       </c>
       <c r="H19">
-        <v>94.011370358663825</v>
+        <v>94.01137035866383</v>
       </c>
       <c r="I19">
-        <v>-0.13685405994742439</v>
+        <v>-0.1368540599474244</v>
       </c>
       <c r="J19">
-        <v>-1.45360213421477E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.00145360213421477</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -1137,19 +1097,19 @@
         <v>23</v>
       </c>
       <c r="G20">
-        <v>28420.738487972219</v>
+        <v>28420.73848797222</v>
       </c>
       <c r="H20">
-        <v>29477.977713350541</v>
+        <v>29477.97771335054</v>
       </c>
       <c r="I20">
         <v>1057.239225378318</v>
       </c>
       <c r="J20">
-        <v>3.7199569104291452E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.03719956910429145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -1169,19 +1129,19 @@
         <v>24</v>
       </c>
       <c r="G21">
-        <v>136344.20549828219</v>
+        <v>136344.2054982822</v>
       </c>
       <c r="H21">
-        <v>137595.42361382351</v>
+        <v>137595.4236138235</v>
       </c>
       <c r="I21">
-        <v>1251.2181155412691</v>
+        <v>1251.218115541269</v>
       </c>
       <c r="J21">
-        <v>9.1769071591167352E-3</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.009176907159116735</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -1201,19 +1161,19 @@
         <v>25</v>
       </c>
       <c r="G22">
-        <v>8317.0560137456159</v>
+        <v>8317.056013745616</v>
       </c>
       <c r="H22">
-        <v>7899.6106728260029</v>
+        <v>7899.610672826003</v>
       </c>
       <c r="I22">
-        <v>-417.44534091961299</v>
+        <v>-417.445340919613</v>
       </c>
       <c r="J22">
-        <v>-5.0191478839351357E-2</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.05019147883935136</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -1236,16 +1196,16 @@
         <v>19646.96893063571</v>
       </c>
       <c r="H23">
-        <v>20716.315654683149</v>
+        <v>20716.31565468315</v>
       </c>
       <c r="I23">
-        <v>1069.3467240474349</v>
+        <v>1069.346724047435</v>
       </c>
       <c r="J23">
-        <v>5.4428076301377547E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.05442807630137755</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -1265,19 +1225,19 @@
         <v>24</v>
       </c>
       <c r="G24">
-        <v>87775.906791907677</v>
+        <v>87775.90679190768</v>
       </c>
       <c r="H24">
-        <v>88145.035130624034</v>
+        <v>88145.03513062403</v>
       </c>
       <c r="I24">
-        <v>369.12833871635672</v>
+        <v>369.1283387163567</v>
       </c>
       <c r="J24">
-        <v>4.2053491921360316E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.004205349192136032</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -1297,19 +1257,19 @@
         <v>25</v>
       </c>
       <c r="G25">
-        <v>7917.1242774566126</v>
+        <v>7917.124277456613</v>
       </c>
       <c r="H25">
-        <v>8094.7952146927983</v>
+        <v>8094.795214692798</v>
       </c>
       <c r="I25">
-        <v>177.67093723618561</v>
+        <v>177.6709372361856</v>
       </c>
       <c r="J25">
-        <v>2.2441347515800611E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.02244134751580061</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -1329,19 +1289,19 @@
         <v>23</v>
       </c>
       <c r="G26">
-        <v>6147.4420638390802</v>
+        <v>6147.44206383908</v>
       </c>
       <c r="H26">
         <v>6300.020290295166</v>
       </c>
       <c r="I26">
-        <v>152.57822645608579</v>
+        <v>152.5782264560858</v>
       </c>
       <c r="J26">
-        <v>2.4819790877508581E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.02481979087750858</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -1361,19 +1321,19 @@
         <v>24</v>
       </c>
       <c r="G27">
-        <v>45578.312199387823</v>
+        <v>45578.31219938782</v>
       </c>
       <c r="H27">
-        <v>46745.444864042824</v>
+        <v>46745.44486404282</v>
       </c>
       <c r="I27">
         <v>1167.132664655001</v>
       </c>
       <c r="J27">
-        <v>2.560719360447658E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.02560719360447658</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -1393,19 +1353,19 @@
         <v>25</v>
       </c>
       <c r="G28">
-        <v>17874.245736773111</v>
+        <v>17874.24573677311</v>
       </c>
       <c r="H28">
-        <v>18650.538845662009</v>
+        <v>18650.53884566201</v>
       </c>
       <c r="I28">
-        <v>776.29310888890177</v>
+        <v>776.2931088889018</v>
       </c>
       <c r="J28">
-        <v>4.3430817743084722E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.04343081774308472</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -1425,19 +1385,19 @@
         <v>23</v>
       </c>
       <c r="G29">
-        <v>3914.0732538330271</v>
+        <v>3914.073253833027</v>
       </c>
       <c r="H29">
         <v>3601.574161102707</v>
       </c>
       <c r="I29">
-        <v>-312.49909273032023</v>
+        <v>-312.4990927303202</v>
       </c>
       <c r="J29">
-        <v>-7.9839868204891612E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.07983986820489161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -1460,16 +1420,16 @@
         <v>15786.09646507664</v>
       </c>
       <c r="H30">
-        <v>13984.248059220041</v>
+        <v>13984.24805922004</v>
       </c>
       <c r="I30">
-        <v>-1801.8484058565921</v>
+        <v>-1801.848405856592</v>
       </c>
       <c r="J30">
-        <v>-0.11414147948752219</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.1141414794875222</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -1489,7 +1449,7 @@
         <v>25</v>
       </c>
       <c r="G31">
-        <v>27188.830281090341</v>
+        <v>27188.83028109034</v>
       </c>
       <c r="H31">
         <v>24138.02477967726</v>
@@ -1507,11 +1467,11 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1543,7 +1503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -1566,16 +1526,16 @@
         <v>3451.96904055808</v>
       </c>
       <c r="H2">
-        <v>3302.0626055758371</v>
+        <v>3302.062605575837</v>
       </c>
       <c r="I2">
-        <v>-149.90643498224381</v>
+        <v>-149.9064349822438</v>
       </c>
       <c r="J2">
-        <v>-4.3426355572994478E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.04342635557299448</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -1595,19 +1555,19 @@
         <v>26</v>
       </c>
       <c r="G3">
-        <v>4414.1387988611759</v>
+        <v>4414.138798861176</v>
       </c>
       <c r="H3">
-        <v>4047.3577264948472</v>
+        <v>4047.357726494847</v>
       </c>
       <c r="I3">
-        <v>-366.78107236632923</v>
+        <v>-366.7810723663292</v>
       </c>
       <c r="J3">
-        <v>-8.3092328782447156E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.08309232878244716</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -1627,7 +1587,7 @@
         <v>27</v>
       </c>
       <c r="G4">
-        <v>13381.560946245831</v>
+        <v>13381.56094624583</v>
       </c>
       <c r="H4">
         <v>12303.05596131204</v>
@@ -1636,10 +1596,10 @@
         <v>-1078.504984933797</v>
       </c>
       <c r="J4">
-        <v>-8.059635114813489E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.08059635114813489</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -1662,16 +1622,16 @@
         <v>1664.428681321303</v>
       </c>
       <c r="H5">
-        <v>1677.0264075332759</v>
+        <v>1677.026407533276</v>
       </c>
       <c r="I5">
         <v>12.5977262119734</v>
       </c>
       <c r="J5">
-        <v>7.5687990439895101E-3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.00756879904398951</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -1691,19 +1651,19 @@
         <v>26</v>
       </c>
       <c r="G6">
-        <v>855.38657767188784</v>
+        <v>855.3865776718878</v>
       </c>
       <c r="H6">
-        <v>824.18591007888006</v>
+        <v>824.1859100788801</v>
       </c>
       <c r="I6">
-        <v>-31.200667593007779</v>
+        <v>-31.20066759300778</v>
       </c>
       <c r="J6">
-        <v>-3.6475516927009628E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.03647551692700963</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -1723,7 +1683,7 @@
         <v>27</v>
       </c>
       <c r="G7">
-        <v>3724.7715835774352</v>
+        <v>3724.771583577435</v>
       </c>
       <c r="H7">
         <v>3606.254127772871</v>
@@ -1732,10 +1692,10 @@
         <v>-118.5174558045637</v>
       </c>
       <c r="J7">
-        <v>-3.1818717777784999E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.031818717777785</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -1755,19 +1715,19 @@
         <v>23</v>
       </c>
       <c r="G8">
-        <v>1144.8958530887819</v>
+        <v>1144.895853088782</v>
       </c>
       <c r="H8">
-        <v>992.23011623224909</v>
+        <v>992.2301162322491</v>
       </c>
       <c r="I8">
-        <v>-152.66573685653259</v>
+        <v>-152.6657368565326</v>
       </c>
       <c r="J8">
-        <v>-0.13334465003490059</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.1333446500349006</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -1793,13 +1753,13 @@
         <v>1329.866189055798</v>
       </c>
       <c r="I9">
-        <v>-262.78596301325553</v>
+        <v>-262.7859630132555</v>
       </c>
       <c r="J9">
-        <v>-0.16499896896623889</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.1649989689662389</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -1819,19 +1779,19 @@
         <v>27</v>
       </c>
       <c r="G10">
-        <v>6285.5915894824984</v>
+        <v>6285.591589482498</v>
       </c>
       <c r="H10">
         <v>5147.580973091025</v>
       </c>
       <c r="I10">
-        <v>-1138.0106163914729</v>
+        <v>-1138.010616391473</v>
       </c>
       <c r="J10">
-        <v>-0.18105067759981011</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.1810506775998101</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -1854,16 +1814,16 @@
         <v>2548.713461124355</v>
       </c>
       <c r="H11">
-        <v>2543.0445734705431</v>
+        <v>2543.044573470543</v>
       </c>
       <c r="I11">
-        <v>-5.6688876538119084</v>
+        <v>-5.668887653811908</v>
       </c>
       <c r="J11">
-        <v>-2.2242153699424099E-3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.00222421536994241</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1886,16 +1846,16 @@
         <v>2369.348836164419</v>
       </c>
       <c r="H12">
-        <v>2211.2847600956329</v>
+        <v>2211.284760095633</v>
       </c>
       <c r="I12">
-        <v>-158.06407606878659</v>
+        <v>-158.0640760687866</v>
       </c>
       <c r="J12">
-        <v>-6.6712032291819864E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.06671203229181986</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -1918,16 +1878,16 @@
         <v>10018.38219735946</v>
       </c>
       <c r="H13">
-        <v>9454.7065199287463</v>
+        <v>9454.706519928746</v>
       </c>
       <c r="I13">
-        <v>-563.67567743071595</v>
+        <v>-563.675677430716</v>
       </c>
       <c r="J13">
-        <v>-5.626414188702878E-2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.05626414188702878</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1947,19 +1907,19 @@
         <v>23</v>
       </c>
       <c r="G14">
-        <v>2443.9877546628109</v>
+        <v>2443.987754662811</v>
       </c>
       <c r="H14">
         <v>2409.001642550224</v>
       </c>
       <c r="I14">
-        <v>-34.986112112586852</v>
+        <v>-34.98611211258685</v>
       </c>
       <c r="J14">
-        <v>-1.431517488000416E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.01431517488000416</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -1979,19 +1939,19 @@
         <v>26</v>
       </c>
       <c r="G15">
-        <v>771.19735551097688</v>
+        <v>771.1973555109769</v>
       </c>
       <c r="H15">
-        <v>741.40448254867613</v>
+        <v>741.4044825486761</v>
       </c>
       <c r="I15">
-        <v>-29.792872962300748</v>
+        <v>-29.79287296230075</v>
       </c>
       <c r="J15">
-        <v>-3.8631969818621457E-2</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.03863196981862146</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -2014,16 +1974,16 @@
         <v>2771.839770532215</v>
       </c>
       <c r="H16">
-        <v>2718.2844379954231</v>
+        <v>2718.284437995423</v>
       </c>
       <c r="I16">
-        <v>-53.555332536792321</v>
+        <v>-53.55533253679232</v>
       </c>
       <c r="J16">
-        <v>-1.932122235424498E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.01932122235424498</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -2043,19 +2003,19 @@
         <v>23</v>
       </c>
       <c r="G17">
-        <v>737.92757910296018</v>
+        <v>737.9275791029602</v>
       </c>
       <c r="H17">
-        <v>756.58045553667444</v>
+        <v>756.5804555366744</v>
       </c>
       <c r="I17">
-        <v>18.652876433714251</v>
+        <v>18.65287643371425</v>
       </c>
       <c r="J17">
-        <v>2.527738081884549E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.02527738081884549</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -2075,19 +2035,19 @@
         <v>26</v>
       </c>
       <c r="G18">
-        <v>76.961772053682168</v>
+        <v>76.96177205368217</v>
       </c>
       <c r="H18">
-        <v>75.151746886196918</v>
+        <v>75.15174688619692</v>
       </c>
       <c r="I18">
-        <v>-1.8100251674852501</v>
+        <v>-1.81002516748525</v>
       </c>
       <c r="J18">
-        <v>-2.351849651048479E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.02351849651048479</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -2107,19 +2067,19 @@
         <v>27</v>
       </c>
       <c r="G19">
-        <v>217.13615426910391</v>
+        <v>217.1361542691039</v>
       </c>
       <c r="H19">
-        <v>216.10942077030171</v>
+        <v>216.1094207703017</v>
       </c>
       <c r="I19">
         <v>-1.026733498802173</v>
       </c>
       <c r="J19">
-        <v>-4.7285239174389582E-3</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.004728523917438958</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -2139,19 +2099,19 @@
         <v>23</v>
       </c>
       <c r="G20">
-        <v>28420.738487972219</v>
+        <v>28420.73848797222</v>
       </c>
       <c r="H20">
-        <v>29477.977713350541</v>
+        <v>29477.97771335054</v>
       </c>
       <c r="I20">
         <v>1057.239225378318</v>
       </c>
       <c r="J20">
-        <v>3.7199569104291452E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.03719956910429145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -2171,19 +2131,19 @@
         <v>26</v>
       </c>
       <c r="G21">
-        <v>19251.159450171741</v>
+        <v>19251.15945017174</v>
       </c>
       <c r="H21">
         <v>18859.45959321535</v>
       </c>
       <c r="I21">
-        <v>-391.69985695639122</v>
+        <v>-391.6998569563912</v>
       </c>
       <c r="J21">
-        <v>-2.0346819004342969E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.02034681900434297</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -2212,10 +2172,10 @@
         <v>1225.472631578057</v>
       </c>
       <c r="J22">
-        <v>9.7717218264730954E-3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.009771721826473095</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -2238,16 +2198,16 @@
         <v>19646.96893063571</v>
       </c>
       <c r="H23">
-        <v>20716.315654683149</v>
+        <v>20716.31565468315</v>
       </c>
       <c r="I23">
-        <v>1069.3467240474349</v>
+        <v>1069.346724047435</v>
       </c>
       <c r="J23">
-        <v>5.4428076301377547E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.05442807630137755</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -2267,19 +2227,19 @@
         <v>26</v>
       </c>
       <c r="G24">
-        <v>60774.346098266084</v>
+        <v>60774.34609826608</v>
       </c>
       <c r="H24">
         <v>60014.07059865597</v>
       </c>
       <c r="I24">
-        <v>-760.27549961011391</v>
+        <v>-760.2754996101139</v>
       </c>
       <c r="J24">
-        <v>-1.2509809622317019E-2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.01250980962231702</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -2299,19 +2259,19 @@
         <v>27</v>
       </c>
       <c r="G25">
-        <v>34918.684971098213</v>
+        <v>34918.68497109821</v>
       </c>
       <c r="H25">
-        <v>36225.759746660857</v>
+        <v>36225.75974666086</v>
       </c>
       <c r="I25">
         <v>1307.074775562643</v>
       </c>
       <c r="J25">
-        <v>3.7431958753443718E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.03743195875344372</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -2331,19 +2291,19 @@
         <v>23</v>
       </c>
       <c r="G26">
-        <v>6147.4420638390802</v>
+        <v>6147.44206383908</v>
       </c>
       <c r="H26">
         <v>6300.020290295166</v>
       </c>
       <c r="I26">
-        <v>152.57822645608579</v>
+        <v>152.5782264560858</v>
       </c>
       <c r="J26">
-        <v>2.4819790877508581E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.02481979087750858</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -2363,19 +2323,19 @@
         <v>26</v>
       </c>
       <c r="G27">
-        <v>34734.062090074352</v>
+        <v>34734.06209007435</v>
       </c>
       <c r="H27">
-        <v>35597.970774322108</v>
+        <v>35597.97077432211</v>
       </c>
       <c r="I27">
-        <v>863.90868424775545</v>
+        <v>863.9086842477554</v>
       </c>
       <c r="J27">
-        <v>2.4872089017616721E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.02487208901761672</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -2395,19 +2355,19 @@
         <v>27</v>
       </c>
       <c r="G28">
-        <v>28718.495846086571</v>
+        <v>28718.49584608657</v>
       </c>
       <c r="H28">
-        <v>29798.012935382721</v>
+        <v>29798.01293538272</v>
       </c>
       <c r="I28">
-        <v>1079.5170892961539</v>
+        <v>1079.517089296154</v>
       </c>
       <c r="J28">
-        <v>3.7589611067435427E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+        <v>0.03758961106743543</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -2427,19 +2387,19 @@
         <v>23</v>
       </c>
       <c r="G29">
-        <v>3914.0732538330271</v>
+        <v>3914.073253833027</v>
       </c>
       <c r="H29">
         <v>3601.574161102707</v>
       </c>
       <c r="I29">
-        <v>-312.49909273032023</v>
+        <v>-312.4990927303202</v>
       </c>
       <c r="J29">
-        <v>-7.9839868204891612E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+        <v>-0.07983986820489161</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -2459,10 +2419,10 @@
         <v>26</v>
       </c>
       <c r="G30">
-        <v>10643.882879045979</v>
+        <v>10643.88287904598</v>
       </c>
       <c r="H30">
-        <v>9488.0847250059651</v>
+        <v>9488.084725005965</v>
       </c>
       <c r="I30">
         <v>-1155.798154040016</v>
@@ -2471,7 +2431,7 @@
         <v>-0.1085880187873329</v>
       </c>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -2491,16 +2451,16 @@
         <v>27</v>
       </c>
       <c r="G31">
-        <v>32331.043867120999</v>
+        <v>32331.043867121</v>
       </c>
       <c r="H31">
-        <v>28634.188113891341</v>
+        <v>28634.18811389134</v>
       </c>
       <c r="I31">
-        <v>-3696.8557532296581</v>
+        <v>-3696.855753229658</v>
       </c>
       <c r="J31">
-        <v>-0.11434384143065569</v>
+        <v>-0.1143438414306557</v>
       </c>
     </row>
   </sheetData>
@@ -2509,18 +2469,11 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="5" max="5" width="25.42578125" customWidth="1"/>
-    <col min="6" max="6" width="29.7109375" customWidth="1"/>
-    <col min="7" max="8" width="11.5703125" style="3" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="10.28515625" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="9.140625" style="5"/>
-  </cols>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2539,20 +2492,20 @@
       <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>10</v>
       </c>
@@ -2571,20 +2524,20 @@
       <c r="F2" t="s">
         <v>28</v>
       </c>
-      <c r="G2" s="3">
-        <v>358.22320232206351</v>
-      </c>
-      <c r="H2" s="3">
-        <v>335.03271423314169</v>
-      </c>
-      <c r="I2" s="3">
-        <v>-23.190488088921771</v>
-      </c>
-      <c r="J2" s="5">
-        <v>-6.4737537765831729E-2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G2">
+        <v>358.2232023220635</v>
+      </c>
+      <c r="H2">
+        <v>335.0327142331417</v>
+      </c>
+      <c r="I2">
+        <v>-23.19048808892177</v>
+      </c>
+      <c r="J2">
+        <v>-0.06473753776583173</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" t="s">
         <v>10</v>
       </c>
@@ -2603,20 +2556,20 @@
       <c r="F3" t="s">
         <v>23</v>
       </c>
-      <c r="G3" s="3">
+      <c r="G3">
         <v>3451.96904055808</v>
       </c>
-      <c r="H3" s="3">
-        <v>3302.0626055758371</v>
-      </c>
-      <c r="I3" s="3">
-        <v>-149.90643498224381</v>
-      </c>
-      <c r="J3" s="5">
-        <v>-4.3426355572994478E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H3">
+        <v>3302.062605575837</v>
+      </c>
+      <c r="I3">
+        <v>-149.9064349822438</v>
+      </c>
+      <c r="J3">
+        <v>-0.04342635557299448</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>10</v>
       </c>
@@ -2635,20 +2588,20 @@
       <c r="F4" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="3">
-        <v>12813.140658263719</v>
-      </c>
-      <c r="H4" s="3">
-        <v>11775.861399610259</v>
-      </c>
-      <c r="I4" s="3">
-        <v>-1037.2792586534581</v>
-      </c>
-      <c r="J4" s="5">
-        <v>-8.095433323636185E-2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G4">
+        <v>12813.14065826372</v>
+      </c>
+      <c r="H4">
+        <v>11775.86139961026</v>
+      </c>
+      <c r="I4">
+        <v>-1037.279258653458</v>
+      </c>
+      <c r="J4">
+        <v>-0.08095433323636185</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
         <v>10</v>
       </c>
@@ -2667,20 +2620,20 @@
       <c r="F5" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="3">
-        <v>4624.3358845212288</v>
-      </c>
-      <c r="H5" s="3">
-        <v>4239.5195739634828</v>
-      </c>
-      <c r="I5" s="3">
-        <v>-384.81631055774602</v>
-      </c>
-      <c r="J5" s="5">
-        <v>-8.3215475728270358E-2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G5">
+        <v>4624.335884521229</v>
+      </c>
+      <c r="H5">
+        <v>4239.519573963483</v>
+      </c>
+      <c r="I5">
+        <v>-384.816310557746</v>
+      </c>
+      <c r="J5">
+        <v>-0.08321547572827036</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -2699,20 +2652,20 @@
       <c r="F6" t="s">
         <v>28</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6">
         <v>109.9026098247154</v>
       </c>
-      <c r="H6" s="3">
-        <v>105.78059334665259</v>
-      </c>
-      <c r="I6" s="3">
-        <v>-4.1220164780628323</v>
-      </c>
-      <c r="J6" s="5">
-        <v>-3.7506083655675433E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H6">
+        <v>105.7805933466526</v>
+      </c>
+      <c r="I6">
+        <v>-4.122016478062832</v>
+      </c>
+      <c r="J6">
+        <v>-0.03750608365567543</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -2731,20 +2684,20 @@
       <c r="F7" t="s">
         <v>23</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7">
         <v>1664.428681321303</v>
       </c>
-      <c r="H7" s="3">
-        <v>1677.0264075332759</v>
-      </c>
-      <c r="I7" s="3">
+      <c r="H7">
+        <v>1677.026407533276</v>
+      </c>
+      <c r="I7">
         <v>12.5977262119734</v>
       </c>
-      <c r="J7" s="5">
-        <v>7.5687990439895101E-3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J7">
+        <v>0.00756879904398951</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
         <v>10</v>
       </c>
@@ -2763,20 +2716,20 @@
       <c r="F8" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="3">
-        <v>3583.0899058515979</v>
-      </c>
-      <c r="H8" s="3">
-        <v>3470.1669157726392</v>
-      </c>
-      <c r="I8" s="3">
+      <c r="G8">
+        <v>3583.089905851598</v>
+      </c>
+      <c r="H8">
+        <v>3470.166915772639</v>
+      </c>
+      <c r="I8">
         <v>-112.9229900789592</v>
       </c>
-      <c r="J8" s="5">
-        <v>-3.1515533532815623E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J8">
+        <v>-0.03151553353281562</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -2795,20 +2748,20 @@
       <c r="F9" t="s">
         <v>30</v>
       </c>
-      <c r="G9" s="3">
-        <v>887.16564557301001</v>
-      </c>
-      <c r="H9" s="3">
+      <c r="G9">
+        <v>887.16564557301</v>
+      </c>
+      <c r="H9">
         <v>854.4925287324603</v>
       </c>
-      <c r="I9" s="3">
+      <c r="I9">
         <v>-32.67311684054971</v>
       </c>
-      <c r="J9" s="5">
-        <v>-3.6828654269458923E-2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J9">
+        <v>-0.03682865426945892</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
         <v>10</v>
       </c>
@@ -2827,20 +2780,20 @@
       <c r="F10" t="s">
         <v>28</v>
       </c>
-      <c r="G10" s="3">
-        <v>68.013615034977093</v>
-      </c>
-      <c r="H10" s="3">
-        <v>55.774322054697762</v>
-      </c>
-      <c r="I10" s="3">
-        <v>-12.239292980279339</v>
-      </c>
-      <c r="J10" s="5">
-        <v>-0.17995357214853361</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G10">
+        <v>68.01361503497709</v>
+      </c>
+      <c r="H10">
+        <v>55.77432205469776</v>
+      </c>
+      <c r="I10">
+        <v>-12.23929298027934</v>
+      </c>
+      <c r="J10">
+        <v>-0.1799535721485336</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -2859,20 +2812,20 @@
       <c r="F11" t="s">
         <v>23</v>
       </c>
-      <c r="G11" s="3">
-        <v>1144.8958530887819</v>
-      </c>
-      <c r="H11" s="3">
-        <v>992.23011623224909</v>
-      </c>
-      <c r="I11" s="3">
-        <v>-152.66573685653259</v>
-      </c>
-      <c r="J11" s="5">
-        <v>-0.13334465003490059</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G11">
+        <v>1144.895853088782</v>
+      </c>
+      <c r="H11">
+        <v>992.2301162322491</v>
+      </c>
+      <c r="I11">
+        <v>-152.6657368565326</v>
+      </c>
+      <c r="J11">
+        <v>-0.1333446500349006</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -2891,20 +2844,20 @@
       <c r="F12" t="s">
         <v>29</v>
       </c>
-      <c r="G12" s="3">
-        <v>6183.5711669300326</v>
-      </c>
-      <c r="H12" s="3">
-        <v>5062.4428290704118</v>
-      </c>
-      <c r="I12" s="3">
-        <v>-1121.1283378596211</v>
-      </c>
-      <c r="J12" s="5">
-        <v>-0.18130758223588611</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G12">
+        <v>6183.571166930033</v>
+      </c>
+      <c r="H12">
+        <v>5062.442829070412</v>
+      </c>
+      <c r="I12">
+        <v>-1121.128337859621</v>
+      </c>
+      <c r="J12">
+        <v>-0.1813075822358861</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -2923,20 +2876,20 @@
       <c r="F13" t="s">
         <v>30</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13">
         <v>1626.658959586543</v>
       </c>
-      <c r="H13" s="3">
-        <v>1359.2300110217141</v>
-      </c>
-      <c r="I13" s="3">
-        <v>-267.42894856482849</v>
-      </c>
-      <c r="J13" s="5">
+      <c r="H13">
+        <v>1359.230011021714</v>
+      </c>
+      <c r="I13">
+        <v>-267.4289485648285</v>
+      </c>
+      <c r="J13">
         <v>-0.1644038210890883</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -2955,20 +2908,20 @@
       <c r="F14" t="s">
         <v>28</v>
       </c>
-      <c r="G14" s="3">
-        <v>257.47502615217491</v>
-      </c>
-      <c r="H14" s="3">
-        <v>251.58209980874079</v>
-      </c>
-      <c r="I14" s="3">
-        <v>-5.8929263434340839</v>
-      </c>
-      <c r="J14" s="5">
-        <v>-2.288737059861954E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G14">
+        <v>257.4750261521749</v>
+      </c>
+      <c r="H14">
+        <v>251.5820998087408</v>
+      </c>
+      <c r="I14">
+        <v>-5.892926343434084</v>
+      </c>
+      <c r="J14">
+        <v>-0.02288737059861954</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
         <v>10</v>
       </c>
@@ -2987,20 +2940,20 @@
       <c r="F15" t="s">
         <v>23</v>
       </c>
-      <c r="G15" s="3">
+      <c r="G15">
         <v>2548.713461124355</v>
       </c>
-      <c r="H15" s="3">
-        <v>2543.0445734705431</v>
-      </c>
-      <c r="I15" s="3">
-        <v>-5.6688876538119084</v>
-      </c>
-      <c r="J15" s="5">
-        <v>-2.2242153699424099E-3</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H15">
+        <v>2543.044573470543</v>
+      </c>
+      <c r="I15">
+        <v>-5.668887653811908</v>
+      </c>
+      <c r="J15">
+        <v>-0.00222421536994241</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
         <v>10</v>
       </c>
@@ -3019,20 +2972,20 @@
       <c r="F16" t="s">
         <v>29</v>
       </c>
-      <c r="G16" s="3">
-        <v>9677.0108143711859</v>
-      </c>
-      <c r="H16" s="3">
+      <c r="G16">
+        <v>9677.010814371186</v>
+      </c>
+      <c r="H16">
         <v>9127.589807616685</v>
       </c>
-      <c r="I16" s="3">
-        <v>-549.42100675450092</v>
-      </c>
-      <c r="J16" s="5">
-        <v>-5.6775900874117442E-2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I16">
+        <v>-549.4210067545009</v>
+      </c>
+      <c r="J16">
+        <v>-0.05677590087411744</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
         <v>10</v>
       </c>
@@ -3051,20 +3004,20 @@
       <c r="F17" t="s">
         <v>30</v>
       </c>
-      <c r="G17" s="3">
-        <v>2453.2451930005218</v>
-      </c>
-      <c r="H17" s="3">
-        <v>2286.8193725989531</v>
-      </c>
-      <c r="I17" s="3">
+      <c r="G17">
+        <v>2453.245193000522</v>
+      </c>
+      <c r="H17">
+        <v>2286.819372598953</v>
+      </c>
+      <c r="I17">
         <v>-166.4258204015691</v>
       </c>
-      <c r="J17" s="5">
-        <v>-6.7839048814365185E-2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J17">
+        <v>-0.06783904881436519</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
         <v>10</v>
       </c>
@@ -3083,20 +3036,20 @@
       <c r="F18" t="s">
         <v>28</v>
       </c>
-      <c r="G18" s="3">
-        <v>197.45632773952551</v>
-      </c>
-      <c r="H18" s="3">
+      <c r="G18">
+        <v>197.4563277395255</v>
+      </c>
+      <c r="H18">
         <v>186.0946485799231</v>
       </c>
-      <c r="I18" s="3">
-        <v>-11.361679159602369</v>
-      </c>
-      <c r="J18" s="5">
-        <v>-5.7540213016572112E-2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I18">
+        <v>-11.36167915960237</v>
+      </c>
+      <c r="J18">
+        <v>-0.05754021301657211</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
         <v>10</v>
       </c>
@@ -3115,20 +3068,20 @@
       <c r="F19" t="s">
         <v>23</v>
       </c>
-      <c r="G19" s="3">
-        <v>2443.9877546628109</v>
-      </c>
-      <c r="H19" s="3">
+      <c r="G19">
+        <v>2443.987754662811</v>
+      </c>
+      <c r="H19">
         <v>2409.001642550224</v>
       </c>
-      <c r="I19" s="3">
-        <v>-34.986112112586852</v>
-      </c>
-      <c r="J19" s="5">
-        <v>-1.431517488000416E-2</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I19">
+        <v>-34.98611211258685</v>
+      </c>
+      <c r="J19">
+        <v>-0.01431517488000416</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
         <v>10</v>
       </c>
@@ -3147,20 +3100,20 @@
       <c r="F20" t="s">
         <v>29</v>
       </c>
-      <c r="G20" s="3">
-        <v>2563.2066695244148</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="G20">
+        <v>2563.206669524415</v>
+      </c>
+      <c r="H20">
         <v>2522.854782450896</v>
       </c>
-      <c r="I20" s="3">
-        <v>-40.351887073519258</v>
-      </c>
-      <c r="J20" s="5">
-        <v>-1.5742736453243651E-2</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I20">
+        <v>-40.35188707351926</v>
+      </c>
+      <c r="J20">
+        <v>-0.01574273645324365</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
         <v>10</v>
       </c>
@@ -3179,20 +3132,20 @@
       <c r="F21" t="s">
         <v>30</v>
       </c>
-      <c r="G21" s="3">
-        <v>782.37412877925146</v>
-      </c>
-      <c r="H21" s="3">
-        <v>750.73948951328009</v>
-      </c>
-      <c r="I21" s="3">
-        <v>-31.634639265971369</v>
-      </c>
-      <c r="J21" s="5">
-        <v>-4.0434158163347389E-2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G21">
+        <v>782.3741287792515</v>
+      </c>
+      <c r="H21">
+        <v>750.7394895132801</v>
+      </c>
+      <c r="I21">
+        <v>-31.63463926597137</v>
+      </c>
+      <c r="J21">
+        <v>-0.04043415816334739</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
         <v>10</v>
       </c>
@@ -3211,20 +3164,20 @@
       <c r="F22" t="s">
         <v>28</v>
       </c>
-      <c r="G22" s="3">
-        <v>75.033535934690434</v>
-      </c>
-      <c r="H22" s="3">
-        <v>75.042092325330799</v>
-      </c>
-      <c r="I22" s="3">
-        <v>8.5563906403649526E-3</v>
-      </c>
-      <c r="J22" s="5">
-        <v>1.140342186167593E-4</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G22">
+        <v>75.03353593469043</v>
+      </c>
+      <c r="H22">
+        <v>75.0420923253308</v>
+      </c>
+      <c r="I22">
+        <v>0.008556390640364953</v>
+      </c>
+      <c r="J22">
+        <v>0.0001140342186167593</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -3243,20 +3196,20 @@
       <c r="F23" t="s">
         <v>23</v>
       </c>
-      <c r="G23" s="3">
-        <v>737.92757910296018</v>
-      </c>
-      <c r="H23" s="3">
-        <v>756.58045553667444</v>
-      </c>
-      <c r="I23" s="3">
-        <v>18.652876433714251</v>
-      </c>
-      <c r="J23" s="5">
-        <v>2.527738081884549E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G23">
+        <v>737.9275791029602</v>
+      </c>
+      <c r="H23">
+        <v>756.5804555366744</v>
+      </c>
+      <c r="I23">
+        <v>18.65287643371425</v>
+      </c>
+      <c r="J23">
+        <v>0.02527738081884549</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
         <v>10</v>
       </c>
@@ -3275,20 +3228,20 @@
       <c r="F24" t="s">
         <v>29</v>
       </c>
-      <c r="G24" s="3">
-        <v>137.91080068443091</v>
-      </c>
-      <c r="H24" s="3">
-        <v>136.69643906440831</v>
-      </c>
-      <c r="I24" s="3">
-        <v>-1.2143616200226011</v>
-      </c>
-      <c r="J24" s="5">
-        <v>-8.8054134556242412E-3</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G24">
+        <v>137.9108006844309</v>
+      </c>
+      <c r="H24">
+        <v>136.6964390644083</v>
+      </c>
+      <c r="I24">
+        <v>-1.214361620022601</v>
+      </c>
+      <c r="J24">
+        <v>-0.008805413455624241</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
         <v>10</v>
       </c>
@@ -3307,20 +3260,20 @@
       <c r="F25" t="s">
         <v>30</v>
       </c>
-      <c r="G25" s="3">
-        <v>81.153589703664721</v>
-      </c>
-      <c r="H25" s="3">
-        <v>79.522636266759548</v>
-      </c>
-      <c r="I25" s="3">
+      <c r="G25">
+        <v>81.15358970366472</v>
+      </c>
+      <c r="H25">
+        <v>79.52263626675955</v>
+      </c>
+      <c r="I25">
         <v>-1.630953436905173</v>
       </c>
-      <c r="J25" s="5">
-        <v>-2.0097120076396611E-2</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J25">
+        <v>-0.02009712007639661</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
         <v>10</v>
       </c>
@@ -3339,20 +3292,20 @@
       <c r="F26" t="s">
         <v>28</v>
       </c>
-      <c r="G26" s="3">
+      <c r="G26">
         <v>2795.482474226756</v>
       </c>
-      <c r="H26" s="3">
+      <c r="H26">
         <v>2720.328558298284</v>
       </c>
-      <c r="I26" s="3">
-        <v>-75.153915928471179</v>
-      </c>
-      <c r="J26" s="5">
-        <v>-2.6884059056481519E-2</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I26">
+        <v>-75.15391592847118</v>
+      </c>
+      <c r="J26">
+        <v>-0.02688405905648152</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
         <v>10</v>
       </c>
@@ -3371,20 +3324,20 @@
       <c r="F27" t="s">
         <v>23</v>
       </c>
-      <c r="G27" s="3">
-        <v>28420.738487972219</v>
-      </c>
-      <c r="H27" s="3">
-        <v>29477.977713350541</v>
-      </c>
-      <c r="I27" s="3">
+      <c r="G27">
+        <v>28420.73848797222</v>
+      </c>
+      <c r="H27">
+        <v>29477.97771335054</v>
+      </c>
+      <c r="I27">
         <v>1057.239225378318</v>
       </c>
-      <c r="J27" s="5">
-        <v>3.7199569104291452E-2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J27">
+        <v>0.03719956910429145</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
         <v>10</v>
       </c>
@@ -3403,20 +3356,20 @@
       <c r="F28" t="s">
         <v>29</v>
       </c>
-      <c r="G28" s="3">
-        <v>122029.74914089389</v>
-      </c>
-      <c r="H28" s="3">
-        <v>123313.79187016679</v>
-      </c>
-      <c r="I28" s="3">
+      <c r="G28">
+        <v>122029.7491408939</v>
+      </c>
+      <c r="H28">
+        <v>123313.7918701668</v>
+      </c>
+      <c r="I28">
         <v>1284.042729272885</v>
       </c>
-      <c r="J28" s="5">
-        <v>1.0522374571059281E-2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J28">
+        <v>0.01052237457105928</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
         <v>10</v>
       </c>
@@ -3435,20 +3388,20 @@
       <c r="F29" t="s">
         <v>30</v>
       </c>
-      <c r="G29" s="3">
-        <v>19836.029896907119</v>
-      </c>
-      <c r="H29" s="3">
-        <v>19460.913858184351</v>
-      </c>
-      <c r="I29" s="3">
-        <v>-375.11603872276828</v>
-      </c>
-      <c r="J29" s="5">
-        <v>-1.891084257648035E-2</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G29">
+        <v>19836.02989690712</v>
+      </c>
+      <c r="H29">
+        <v>19460.91385818435</v>
+      </c>
+      <c r="I29">
+        <v>-375.1160387227683</v>
+      </c>
+      <c r="J29">
+        <v>-0.01891084257648035</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
         <v>10</v>
       </c>
@@ -3467,20 +3420,20 @@
       <c r="F30" t="s">
         <v>28</v>
       </c>
-      <c r="G30" s="3">
-        <v>822.96423410401496</v>
-      </c>
-      <c r="H30" s="3">
-        <v>879.25728060789709</v>
-      </c>
-      <c r="I30" s="3">
-        <v>56.293046503882117</v>
-      </c>
-      <c r="J30" s="5">
-        <v>6.8402786137079216E-2</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G30">
+        <v>822.964234104015</v>
+      </c>
+      <c r="H30">
+        <v>879.2572806078971</v>
+      </c>
+      <c r="I30">
+        <v>56.29304650388212</v>
+      </c>
+      <c r="J30">
+        <v>0.06840278613707922</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
         <v>10</v>
       </c>
@@ -3499,20 +3452,20 @@
       <c r="F31" t="s">
         <v>23</v>
       </c>
-      <c r="G31" s="3">
+      <c r="G31">
         <v>19646.96893063571</v>
       </c>
-      <c r="H31" s="3">
-        <v>20716.315654683149</v>
-      </c>
-      <c r="I31" s="3">
-        <v>1069.3467240474349</v>
-      </c>
-      <c r="J31" s="5">
-        <v>5.4428076301377547E-2</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H31">
+        <v>20716.31565468315</v>
+      </c>
+      <c r="I31">
+        <v>1069.346724047435</v>
+      </c>
+      <c r="J31">
+        <v>0.05442807630137755</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
         <v>10</v>
       </c>
@@ -3531,20 +3484,20 @@
       <c r="F32" t="s">
         <v>29</v>
       </c>
-      <c r="G32" s="3">
-        <v>29126.683526011529</v>
-      </c>
-      <c r="H32" s="3">
-        <v>30214.847495216269</v>
-      </c>
-      <c r="I32" s="3">
+      <c r="G32">
+        <v>29126.68352601153</v>
+      </c>
+      <c r="H32">
+        <v>30214.84749521627</v>
+      </c>
+      <c r="I32">
         <v>1088.163969204739</v>
       </c>
-      <c r="J32" s="5">
-        <v>3.7359693500049751E-2</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="J32">
+        <v>0.03735969350004975</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
         <v>10</v>
       </c>
@@ -3563,20 +3516,20 @@
       <c r="F33" t="s">
         <v>30</v>
       </c>
-      <c r="G33" s="3">
-        <v>65743.383309248748</v>
-      </c>
-      <c r="H33" s="3">
-        <v>65145.725569492657</v>
-      </c>
-      <c r="I33" s="3">
-        <v>-597.65773975609045</v>
-      </c>
-      <c r="J33" s="5">
-        <v>-9.0907663961372707E-3</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G33">
+        <v>65743.38330924875</v>
+      </c>
+      <c r="H33">
+        <v>65145.72556949266</v>
+      </c>
+      <c r="I33">
+        <v>-597.6577397560905</v>
+      </c>
+      <c r="J33">
+        <v>-0.009090766396137271</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
         <v>10</v>
       </c>
@@ -3595,20 +3548,20 @@
       <c r="F34" t="s">
         <v>28</v>
       </c>
-      <c r="G34" s="3">
+      <c r="G34">
         <v>50.72146917358625</v>
       </c>
-      <c r="H34" s="3">
-        <v>51.509195733972057</v>
-      </c>
-      <c r="I34" s="3">
-        <v>0.78772656038580635</v>
-      </c>
-      <c r="J34" s="5">
-        <v>1.553043658277989E-2</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="H34">
+        <v>51.50919573397206</v>
+      </c>
+      <c r="I34">
+        <v>0.7877265603858064</v>
+      </c>
+      <c r="J34">
+        <v>0.01553043658277989</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
         <v>10</v>
       </c>
@@ -3627,20 +3580,20 @@
       <c r="F35" t="s">
         <v>23</v>
       </c>
-      <c r="G35" s="3">
-        <v>6147.4420638390802</v>
-      </c>
-      <c r="H35" s="3">
+      <c r="G35">
+        <v>6147.44206383908</v>
+      </c>
+      <c r="H35">
         <v>6300.020290295166</v>
       </c>
-      <c r="I35" s="3">
-        <v>152.57822645608579</v>
-      </c>
-      <c r="J35" s="5">
-        <v>2.4819790877508581E-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I35">
+        <v>152.5782264560858</v>
+      </c>
+      <c r="J35">
+        <v>0.02481979087750858</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
         <v>10</v>
       </c>
@@ -3659,20 +3612,20 @@
       <c r="F36" t="s">
         <v>29</v>
       </c>
-      <c r="G36" s="3">
+      <c r="G36">
         <v>12365.89418452115</v>
       </c>
-      <c r="H36" s="3">
+      <c r="H36">
         <v>12631.42596981273</v>
       </c>
-      <c r="I36" s="3">
-        <v>265.53178529157782</v>
-      </c>
-      <c r="J36" s="5">
-        <v>2.147291423728611E-2</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I36">
+        <v>265.5317852915778</v>
+      </c>
+      <c r="J36">
+        <v>0.02147291423728611</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
         <v>10</v>
       </c>
@@ -3691,20 +3644,20 @@
       <c r="F37" t="s">
         <v>30</v>
       </c>
-      <c r="G37" s="3">
-        <v>51035.942282466181</v>
-      </c>
-      <c r="H37" s="3">
-        <v>52713.048544158133</v>
-      </c>
-      <c r="I37" s="3">
-        <v>1677.1062616919439</v>
-      </c>
-      <c r="J37" s="5">
-        <v>3.2861277497528013E-2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G37">
+        <v>51035.94228246618</v>
+      </c>
+      <c r="H37">
+        <v>52713.04854415813</v>
+      </c>
+      <c r="I37">
+        <v>1677.106261691944</v>
+      </c>
+      <c r="J37">
+        <v>0.03286127749752801</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
         <v>10</v>
       </c>
@@ -3723,20 +3676,20 @@
       <c r="F38" t="s">
         <v>28</v>
       </c>
-      <c r="G38" s="3">
-        <v>129.80344974446129</v>
-      </c>
-      <c r="H38" s="3">
+      <c r="G38">
+        <v>129.8034497444613</v>
+      </c>
+      <c r="H38">
         <v>104.1471664191177</v>
       </c>
-      <c r="I38" s="3">
-        <v>-25.656283325343519</v>
-      </c>
-      <c r="J38" s="5">
-        <v>-0.19765486491963041</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I38">
+        <v>-25.65628332534352</v>
+      </c>
+      <c r="J38">
+        <v>-0.1976548649196304</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
         <v>10</v>
       </c>
@@ -3755,20 +3708,20 @@
       <c r="F39" t="s">
         <v>23</v>
       </c>
-      <c r="G39" s="3">
-        <v>3914.0732538330271</v>
-      </c>
-      <c r="H39" s="3">
+      <c r="G39">
+        <v>3914.073253833027</v>
+      </c>
+      <c r="H39">
         <v>3601.574161102707</v>
       </c>
-      <c r="I39" s="3">
-        <v>-312.49909273032023</v>
-      </c>
-      <c r="J39" s="5">
-        <v>-7.9839868204891612E-2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I39">
+        <v>-312.4990927303202</v>
+      </c>
+      <c r="J39">
+        <v>-0.07983986820489161</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
         <v>10</v>
       </c>
@@ -3787,20 +3740,20 @@
       <c r="F40" t="s">
         <v>29</v>
       </c>
-      <c r="G40" s="3">
-        <v>5821.1854770016926</v>
-      </c>
-      <c r="H40" s="3">
-        <v>5062.7784844735897</v>
-      </c>
-      <c r="I40" s="3">
-        <v>-758.40699252810282</v>
-      </c>
-      <c r="J40" s="5">
-        <v>-0.13028394225272719</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="G40">
+        <v>5821.185477001693</v>
+      </c>
+      <c r="H40">
+        <v>5062.77848447359</v>
+      </c>
+      <c r="I40">
+        <v>-758.4069925281028</v>
+      </c>
+      <c r="J40">
+        <v>-0.1302839422527272</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
         <v>10</v>
       </c>
@@ -3819,16 +3772,16 @@
       <c r="F41" t="s">
         <v>30</v>
       </c>
-      <c r="G41" s="3">
-        <v>37023.937819420833</v>
-      </c>
-      <c r="H41" s="3">
-        <v>32955.347188004591</v>
-      </c>
-      <c r="I41" s="3">
-        <v>-4068.5906314162348</v>
-      </c>
-      <c r="J41" s="5">
+      <c r="G41">
+        <v>37023.93781942083</v>
+      </c>
+      <c r="H41">
+        <v>32955.34718800459</v>
+      </c>
+      <c r="I41">
+        <v>-4068.590631416235</v>
+      </c>
+      <c r="J41">
         <v>-0.1098908131074611</v>
       </c>
     </row>

--- a/data/processed/sam_auto_dashboard_2024_refresh/occ_change_by_education/segment_occ_change_by_education_2024_2030.xlsx
+++ b/data/processed/sam_auto_dashboard_2024_refresh/occ_change_by_education/segment_occ_change_by_education_2024_2030.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="530" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="34">
   <si>
     <t>methodology</t>
   </si>
@@ -46,6 +46,15 @@
   </si>
   <si>
     <t>pct_change</t>
+  </si>
+  <si>
+    <t>share_base</t>
+  </si>
+  <si>
+    <t>share_target</t>
+  </si>
+  <si>
+    <t>share_change</t>
   </si>
   <si>
     <t>sam_mi_moodys_mi</t>
@@ -90,16 +99,16 @@
     <t>BA+</t>
   </si>
   <si>
+    <t>SC or Associate's</t>
+  </si>
+  <si>
     <t>HS or Less</t>
   </si>
   <si>
-    <t>SC or Associate's</t>
+    <t>SC/Associate or Employer Training</t>
   </si>
   <si>
     <t>HS or Less - Limited Training</t>
-  </si>
-  <si>
-    <t>SC/Associate or Employer Training</t>
   </si>
   <si>
     <t>Associate's</t>
@@ -466,10 +475,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,25 +509,34 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G2">
         <v>3451.96904055808</v>
@@ -532,89 +550,116 @@
       <c r="J2">
         <v>-0.04342635557299448</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2">
+        <v>0.1624634248293149</v>
+      </c>
+      <c r="L2">
+        <v>0.1680227242756014</v>
+      </c>
+      <c r="M2">
+        <v>0.09397388447319011</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G3">
-        <v>16795.04319647182</v>
+        <v>1000.656548635188</v>
       </c>
       <c r="H3">
-        <v>15430.95372287424</v>
+        <v>919.4599649326431</v>
       </c>
       <c r="I3">
-        <v>-1364.089473597583</v>
+        <v>-81.19658370254444</v>
       </c>
       <c r="J3">
-        <v>-0.08121976571540711</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>-0.08114330917365188</v>
+      </c>
+      <c r="K3">
+        <v>0.04709488644280301</v>
+      </c>
+      <c r="L3">
+        <v>0.04678595975420354</v>
+      </c>
+      <c r="M3">
+        <v>0.05090080607536579</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G4">
-        <v>1000.656548635188</v>
+        <v>16795.04319647182</v>
       </c>
       <c r="H4">
-        <v>919.4599649326431</v>
+        <v>15430.95372287424</v>
       </c>
       <c r="I4">
-        <v>-81.19658370254444</v>
+        <v>-1364.089473597583</v>
       </c>
       <c r="J4">
-        <v>-0.08114330917365188</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>-0.08121976571540711</v>
+      </c>
+      <c r="K4">
+        <v>0.7904416887278821</v>
+      </c>
+      <c r="L4">
+        <v>0.7851913159701951</v>
+      </c>
+      <c r="M4">
+        <v>0.855125309451444</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G5">
         <v>1664.428681321303</v>
@@ -628,89 +673,116 @@
       <c r="J5">
         <v>0.00756879904398951</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5">
+        <v>0.2665394402035619</v>
+      </c>
+      <c r="L5">
+        <v>0.2745862662578333</v>
+      </c>
+      <c r="M5">
+        <v>-0.0918734664611702</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G6">
-        <v>3887.639306570689</v>
+        <v>692.5188546786338</v>
       </c>
       <c r="H6">
-        <v>3774.373398713734</v>
+        <v>656.0666391380176</v>
       </c>
       <c r="I6">
-        <v>-113.2659078569554</v>
+        <v>-36.45221554061618</v>
       </c>
       <c r="J6">
-        <v>-0.02913488081713733</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>-0.05263714524788207</v>
+      </c>
+      <c r="K6">
+        <v>0.1108990670059372</v>
+      </c>
+      <c r="L6">
+        <v>0.1074204246564072</v>
+      </c>
+      <c r="M6">
+        <v>0.2658409418933974</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>692.5188546786338</v>
+        <v>3887.639306570689</v>
       </c>
       <c r="H7">
-        <v>656.0666391380176</v>
+        <v>3774.373398713734</v>
       </c>
       <c r="I7">
-        <v>-36.45221554061618</v>
+        <v>-113.2659078569554</v>
       </c>
       <c r="J7">
-        <v>-0.05263714524788207</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>-0.02913488081713733</v>
+      </c>
+      <c r="K7">
+        <v>0.6225614927905009</v>
+      </c>
+      <c r="L7">
+        <v>0.6179933090857594</v>
+      </c>
+      <c r="M7">
+        <v>0.8260325245677729</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G8">
         <v>1144.895853088782</v>
@@ -724,89 +796,116 @@
       <c r="J8">
         <v>-0.1333446500349006</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8">
+        <v>0.1268844221105523</v>
+      </c>
+      <c r="L8">
+        <v>0.1328344022444252</v>
+      </c>
+      <c r="M8">
+        <v>0.09827450286914931</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G9">
-        <v>7470.162051341688</v>
+        <v>408.0816902098634</v>
       </c>
       <c r="H9">
-        <v>6145.380291756315</v>
+        <v>332.0668703905082</v>
       </c>
       <c r="I9">
-        <v>-1324.781759585373</v>
+        <v>-76.01481981935524</v>
       </c>
       <c r="J9">
-        <v>-0.1773431085537741</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>-0.1862735369976125</v>
+      </c>
+      <c r="K9">
+        <v>0.04522613065326623</v>
+      </c>
+      <c r="L9">
+        <v>0.04445531687850469</v>
+      </c>
+      <c r="M9">
+        <v>0.04893251611168861</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G10">
-        <v>408.0816902098634</v>
+        <v>7470.162051341688</v>
       </c>
       <c r="H10">
-        <v>332.0668703905082</v>
+        <v>6145.380291756315</v>
       </c>
       <c r="I10">
-        <v>-76.01481981935524</v>
+        <v>-1324.781759585373</v>
       </c>
       <c r="J10">
-        <v>-0.1862735369976125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>-0.1773431085537741</v>
+      </c>
+      <c r="K10">
+        <v>0.8278894472361815</v>
+      </c>
+      <c r="L10">
+        <v>0.8227102808770701</v>
+      </c>
+      <c r="M10">
+        <v>0.8527929810191622</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G11">
         <v>2548.713461124355</v>
@@ -820,89 +919,116 @@
       <c r="J11">
         <v>-0.00222421536994241</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11">
+        <v>0.1706372264187481</v>
+      </c>
+      <c r="L11">
+        <v>0.1789737600560029</v>
+      </c>
+      <c r="M11">
+        <v>0.00779326410643654</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G12">
-        <v>11600.84106595768</v>
+        <v>786.889967566202</v>
       </c>
       <c r="H12">
-        <v>10915.53795803819</v>
+        <v>750.4533219861942</v>
       </c>
       <c r="I12">
-        <v>-685.3031079194952</v>
+        <v>-36.43664558000785</v>
       </c>
       <c r="J12">
-        <v>-0.05907357096120355</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>-0.0463046259093936</v>
+      </c>
+      <c r="K12">
+        <v>0.05268254890567475</v>
+      </c>
+      <c r="L12">
+        <v>0.05281521770540181</v>
+      </c>
+      <c r="M12">
+        <v>0.05009102658202839</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G13">
-        <v>786.889967566202</v>
+        <v>11600.84106595768</v>
       </c>
       <c r="H13">
-        <v>750.4533219861942</v>
+        <v>10915.53795803819</v>
       </c>
       <c r="I13">
-        <v>-36.43664558000785</v>
+        <v>-685.3031079194952</v>
       </c>
       <c r="J13">
-        <v>-0.0463046259093936</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>-0.05907357096120355</v>
+      </c>
+      <c r="K13">
+        <v>0.7766802246755772</v>
+      </c>
+      <c r="L13">
+        <v>0.7682110222385953</v>
+      </c>
+      <c r="M13">
+        <v>0.9421157093115351</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G14">
         <v>2443.987754662811</v>
@@ -916,89 +1042,116 @@
       <c r="J14">
         <v>-0.01431517488000416</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14">
+        <v>0.4082140634723086</v>
+      </c>
+      <c r="L14">
+        <v>0.4104836703607108</v>
+      </c>
+      <c r="M14">
+        <v>0.2956548262474077</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G15">
-        <v>3200.282745816092</v>
+        <v>342.7543802271001</v>
       </c>
       <c r="H15">
-        <v>3140.045112583321</v>
+        <v>319.6438079607781</v>
       </c>
       <c r="I15">
-        <v>-60.23763323277126</v>
+        <v>-23.11057226632204</v>
       </c>
       <c r="J15">
-        <v>-0.01882259725692153</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>-0.06742604500344992</v>
+      </c>
+      <c r="K15">
+        <v>0.05724953329184791</v>
+      </c>
+      <c r="L15">
+        <v>0.05446595020205714</v>
+      </c>
+      <c r="M15">
+        <v>0.1952989862345808</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G16">
-        <v>342.7543802271001</v>
+        <v>3200.282745816092</v>
       </c>
       <c r="H16">
-        <v>319.6438079607781</v>
+        <v>3140.045112583321</v>
       </c>
       <c r="I16">
-        <v>-23.11057226632204</v>
+        <v>-60.23763323277126</v>
       </c>
       <c r="J16">
-        <v>-0.06742604500344992</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>-0.01882259725692153</v>
+      </c>
+      <c r="K16">
+        <v>0.5345364032358435</v>
+      </c>
+      <c r="L16">
+        <v>0.5350503794372321</v>
+      </c>
+      <c r="M16">
+        <v>0.5090461875180115</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G17">
         <v>737.9275791029602</v>
@@ -1012,89 +1165,116 @@
       <c r="J17">
         <v>0.02527738081884549</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17">
+        <v>0.7150284321689701</v>
+      </c>
+      <c r="L17">
+        <v>0.7220370319238563</v>
+      </c>
+      <c r="M17">
+        <v>1.179358721779987</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D18">
         <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G18">
-        <v>199.9497019041748</v>
+        <v>94.14822441861125</v>
       </c>
       <c r="H18">
-        <v>197.2497972978348</v>
+        <v>94.01137035866383</v>
       </c>
       <c r="I18">
-        <v>-2.699904606339999</v>
+        <v>-0.1368540599474244</v>
       </c>
       <c r="J18">
-        <v>-0.01350291888724055</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>-0.00145360213421477</v>
+      </c>
+      <c r="K18">
+        <v>0.09122664500406108</v>
+      </c>
+      <c r="L18">
+        <v>0.08971906467331897</v>
+      </c>
+      <c r="M18">
+        <v>-0.008652822516867839</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D19">
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G19">
-        <v>94.14822441861125</v>
+        <v>199.9497019041748</v>
       </c>
       <c r="H19">
-        <v>94.01137035866383</v>
+        <v>197.2497972978348</v>
       </c>
       <c r="I19">
-        <v>-0.1368540599474244</v>
+        <v>-2.699904606339999</v>
       </c>
       <c r="J19">
-        <v>-0.00145360213421477</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>-0.01350291888724055</v>
+      </c>
+      <c r="K19">
+        <v>0.1937449228269689</v>
+      </c>
+      <c r="L19">
+        <v>0.1882439034028248</v>
+      </c>
+      <c r="M19">
+        <v>-0.1707058992631195</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G20">
         <v>28420.73848797222</v>
@@ -1108,89 +1288,116 @@
       <c r="J20">
         <v>0.03719956910429145</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20">
+        <v>0.1642038946162641</v>
+      </c>
+      <c r="L20">
+        <v>0.1684715681373224</v>
+      </c>
+      <c r="M20">
+        <v>0.5590864708306096</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D21">
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G21">
-        <v>136344.2054982822</v>
+        <v>8317.056013745616</v>
       </c>
       <c r="H21">
-        <v>137595.4236138235</v>
+        <v>7899.610672826003</v>
       </c>
       <c r="I21">
-        <v>1251.218115541269</v>
+        <v>-417.445340919613</v>
       </c>
       <c r="J21">
-        <v>0.009176907159116735</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>-0.05019147883935136</v>
+      </c>
+      <c r="K21">
+        <v>0.04805269186712435</v>
+      </c>
+      <c r="L21">
+        <v>0.04514759494924853</v>
+      </c>
+      <c r="M21">
+        <v>-0.2207523489642682</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D22">
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G22">
-        <v>8317.056013745616</v>
+        <v>136344.2054982822</v>
       </c>
       <c r="H22">
-        <v>7899.610672826003</v>
+        <v>137595.4236138235</v>
       </c>
       <c r="I22">
-        <v>-417.445340919613</v>
+        <v>1251.218115541269</v>
       </c>
       <c r="J22">
-        <v>-0.05019147883935136</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>0.009176907159116735</v>
+      </c>
+      <c r="K22">
+        <v>0.7877434135166117</v>
+      </c>
+      <c r="L22">
+        <v>0.7863808369134291</v>
+      </c>
+      <c r="M22">
+        <v>0.6616658781336586</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D23">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G23">
         <v>19646.96893063571</v>
@@ -1204,89 +1411,116 @@
       <c r="J23">
         <v>0.05442807630137755</v>
       </c>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="K23">
+        <v>0.1703395953757215</v>
+      </c>
+      <c r="L23">
+        <v>0.1771289185151771</v>
+      </c>
+      <c r="M23">
+        <v>0.6616646788393189</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D24">
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G24">
-        <v>87775.90679190768</v>
+        <v>7917.124277456613</v>
       </c>
       <c r="H24">
-        <v>88145.03513062403</v>
+        <v>8094.795214692798</v>
       </c>
       <c r="I24">
-        <v>369.1283387163567</v>
+        <v>177.6709372361856</v>
       </c>
       <c r="J24">
-        <v>0.004205349192136032</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>0.02244134751580061</v>
+      </c>
+      <c r="K24">
+        <v>0.06864161849710952</v>
+      </c>
+      <c r="L24">
+        <v>0.06921222604832412</v>
+      </c>
+      <c r="M24">
+        <v>0.1099349546613908</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D25">
         <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G25">
-        <v>7917.124277456613</v>
+        <v>87775.90679190768</v>
       </c>
       <c r="H25">
-        <v>8094.795214692798</v>
+        <v>88145.03513062403</v>
       </c>
       <c r="I25">
-        <v>177.6709372361856</v>
+        <v>369.1283387163567</v>
       </c>
       <c r="J25">
-        <v>0.02244134751580061</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>0.004205349192136032</v>
+      </c>
+      <c r="K25">
+        <v>0.761018786127169</v>
+      </c>
+      <c r="L25">
+        <v>0.7536588554364988</v>
+      </c>
+      <c r="M25">
+        <v>0.2284003664992902</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D26">
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G26">
         <v>6147.44206383908</v>
@@ -1300,89 +1534,116 @@
       <c r="J26">
         <v>0.02481979087750858</v>
       </c>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="K26">
+        <v>0.08832531700918218</v>
+      </c>
+      <c r="L26">
+        <v>0.08787128903718494</v>
+      </c>
+      <c r="M26">
+        <v>0.0727948164488649</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D27">
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G27">
-        <v>45578.31219938782</v>
+        <v>17874.24573677311</v>
       </c>
       <c r="H27">
-        <v>46745.44486404282</v>
+        <v>18650.53884566201</v>
       </c>
       <c r="I27">
-        <v>1167.132664655001</v>
+        <v>776.2931088889018</v>
       </c>
       <c r="J27">
-        <v>0.02560719360447658</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>0.04343081774308472</v>
+      </c>
+      <c r="K27">
+        <v>0.2568138755283492</v>
+      </c>
+      <c r="L27">
+        <v>0.2601335891141439</v>
+      </c>
+      <c r="M27">
+        <v>0.3703681428513048</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D28">
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G28">
-        <v>17874.24573677311</v>
+        <v>45578.31219938782</v>
       </c>
       <c r="H28">
-        <v>18650.53884566201</v>
+        <v>46745.44486404282</v>
       </c>
       <c r="I28">
-        <v>776.2931088889018</v>
+        <v>1167.132664655001</v>
       </c>
       <c r="J28">
-        <v>0.04343081774308472</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>0.02560719360447658</v>
+      </c>
+      <c r="K28">
+        <v>0.6548608074624687</v>
+      </c>
+      <c r="L28">
+        <v>0.6519951218486713</v>
+      </c>
+      <c r="M28">
+        <v>0.5568370406998303</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D29">
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G29">
         <v>3914.073253833027</v>
@@ -1396,69 +1657,96 @@
       <c r="J29">
         <v>-0.07983986820489161</v>
       </c>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="K29">
+        <v>0.08347529812606426</v>
+      </c>
+      <c r="L29">
+        <v>0.08631932144470537</v>
+      </c>
+      <c r="M29">
+        <v>0.06050142033165728</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D30">
         <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F30" t="s">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="G30">
-        <v>15786.09646507664</v>
+        <v>27188.83028109034</v>
       </c>
       <c r="H30">
-        <v>13984.24805922004</v>
+        <v>24138.02477967726</v>
       </c>
       <c r="I30">
-        <v>-1801.848405856592</v>
+        <v>-3050.80550141308</v>
       </c>
       <c r="J30">
-        <v>-0.1141414794875222</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>-0.1122080453580563</v>
+      </c>
+      <c r="K30">
+        <v>0.5798551959114151</v>
+      </c>
+      <c r="L30">
+        <v>0.5785186773328274</v>
+      </c>
+      <c r="M30">
+        <v>0.5906515259883075</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D31">
         <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F31" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="G31">
-        <v>27188.83028109034</v>
+        <v>15786.09646507664</v>
       </c>
       <c r="H31">
-        <v>24138.02477967726</v>
+        <v>13984.24805922004</v>
       </c>
       <c r="I31">
-        <v>-3050.80550141308</v>
+        <v>-1801.848405856592</v>
       </c>
       <c r="J31">
-        <v>-0.1122080453580563</v>
+        <v>-0.1141414794875222</v>
+      </c>
+      <c r="K31">
+        <v>0.3366695059625208</v>
+      </c>
+      <c r="L31">
+        <v>0.3351620012224674</v>
+      </c>
+      <c r="M31">
+        <v>0.3488470536800351</v>
       </c>
     </row>
   </sheetData>
@@ -1468,10 +1756,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1502,25 +1790,34 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G2">
         <v>3451.96904055808</v>
@@ -1534,89 +1831,116 @@
       <c r="J2">
         <v>-0.04342635557299448</v>
       </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="K2">
+        <v>0.1624634248293149</v>
+      </c>
+      <c r="L2">
+        <v>0.1680227242756013</v>
+      </c>
+      <c r="M2">
+        <v>0.09397388447319019</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G3">
-        <v>4414.138798861176</v>
+        <v>13381.56094624583</v>
       </c>
       <c r="H3">
-        <v>4047.357726494847</v>
+        <v>12303.05596131204</v>
       </c>
       <c r="I3">
-        <v>-366.7810723663292</v>
+        <v>-1078.504984933797</v>
       </c>
       <c r="J3">
-        <v>-0.08309232878244716</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>-0.08059635114813489</v>
+      </c>
+      <c r="K3">
+        <v>0.6297896056848274</v>
+      </c>
+      <c r="L3">
+        <v>0.6260308257160782</v>
+      </c>
+      <c r="M3">
+        <v>0.6760970792877125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G4">
-        <v>13381.56094624583</v>
+        <v>4414.138798861176</v>
       </c>
       <c r="H4">
-        <v>12303.05596131204</v>
+        <v>4047.357726494847</v>
       </c>
       <c r="I4">
-        <v>-1078.504984933797</v>
+        <v>-366.7810723663292</v>
       </c>
       <c r="J4">
-        <v>-0.08059635114813489</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+        <v>-0.08309232878244716</v>
+      </c>
+      <c r="K4">
+        <v>0.2077469694858577</v>
+      </c>
+      <c r="L4">
+        <v>0.2059464500083204</v>
+      </c>
+      <c r="M4">
+        <v>0.2299290362390974</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>2</v>
       </c>
       <c r="E5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F5" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G5">
         <v>1664.428681321303</v>
@@ -1630,89 +1954,116 @@
       <c r="J5">
         <v>0.00756879904398951</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5">
+        <v>0.2665394402035619</v>
+      </c>
+      <c r="L5">
+        <v>0.2745862662578333</v>
+      </c>
+      <c r="M5">
+        <v>-0.09187346646117028</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G6">
-        <v>855.3865776718878</v>
+        <v>3724.771583577435</v>
       </c>
       <c r="H6">
-        <v>824.1859100788801</v>
+        <v>3606.254127772871</v>
       </c>
       <c r="I6">
-        <v>-31.20066759300778</v>
+        <v>-118.5174558045637</v>
       </c>
       <c r="J6">
-        <v>-0.03647551692700963</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>-0.031818717777785</v>
+      </c>
+      <c r="K6">
+        <v>0.5964800678541141</v>
+      </c>
+      <c r="L6">
+        <v>0.5904664659267769</v>
+      </c>
+      <c r="M6">
+        <v>0.864331333901735</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>3724.771583577435</v>
+        <v>855.3865776718878</v>
       </c>
       <c r="H7">
-        <v>3606.254127772871</v>
+        <v>824.1859100788801</v>
       </c>
       <c r="I7">
-        <v>-118.5174558045637</v>
+        <v>-31.20066759300778</v>
       </c>
       <c r="J7">
-        <v>-0.031818717777785</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>-0.03647551692700963</v>
+      </c>
+      <c r="K7">
+        <v>0.136980491942324</v>
+      </c>
+      <c r="L7">
+        <v>0.1349472678153898</v>
+      </c>
+      <c r="M7">
+        <v>0.2275421325594353</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>3</v>
       </c>
       <c r="E8" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G8">
         <v>1144.895853088782</v>
@@ -1726,89 +2077,116 @@
       <c r="J8">
         <v>-0.1333446500349006</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8">
+        <v>0.1268844221105523</v>
+      </c>
+      <c r="L8">
+        <v>0.1328344022444252</v>
+      </c>
+      <c r="M8">
+        <v>0.09827450286914925</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F9" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G9">
-        <v>1592.652152069054</v>
+        <v>6285.591589482498</v>
       </c>
       <c r="H9">
-        <v>1329.866189055798</v>
+        <v>5147.580973091025</v>
       </c>
       <c r="I9">
-        <v>-262.7859630132555</v>
+        <v>-1138.010616391473</v>
       </c>
       <c r="J9">
-        <v>-0.1649989689662389</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+        <v>-0.1810506775998101</v>
+      </c>
+      <c r="K9">
+        <v>0.6966080402010055</v>
+      </c>
+      <c r="L9">
+        <v>0.6891303039276758</v>
+      </c>
+      <c r="M9">
+        <v>0.7325640309900395</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G10">
-        <v>6285.591589482498</v>
+        <v>1592.652152069054</v>
       </c>
       <c r="H10">
-        <v>5147.580973091025</v>
+        <v>1329.866189055798</v>
       </c>
       <c r="I10">
-        <v>-1138.010616391473</v>
+        <v>-262.7859630132555</v>
       </c>
       <c r="J10">
-        <v>-0.1810506775998101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>-0.1649989689662389</v>
+      </c>
+      <c r="K10">
+        <v>0.1765075376884422</v>
+      </c>
+      <c r="L10">
+        <v>0.1780352938278989</v>
+      </c>
+      <c r="M10">
+        <v>0.1691614661408112</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>4</v>
       </c>
       <c r="E11" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G11">
         <v>2548.713461124355</v>
@@ -1822,89 +2200,116 @@
       <c r="J11">
         <v>-0.00222421536994241</v>
       </c>
-    </row>
-    <row r="12" spans="1:10">
+      <c r="K11">
+        <v>0.1706372264187481</v>
+      </c>
+      <c r="L11">
+        <v>0.1789737600560029</v>
+      </c>
+      <c r="M11">
+        <v>0.007793264106436546</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>4</v>
       </c>
       <c r="E12" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G12">
-        <v>2369.348836164419</v>
+        <v>10018.38219735946</v>
       </c>
       <c r="H12">
-        <v>2211.284760095633</v>
+        <v>9454.706519928746</v>
       </c>
       <c r="I12">
-        <v>-158.0640760687866</v>
+        <v>-563.675677430716</v>
       </c>
       <c r="J12">
-        <v>-0.06671203229181986</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
+        <v>-0.05626414188702878</v>
+      </c>
+      <c r="K12">
+        <v>0.6707340693395321</v>
+      </c>
+      <c r="L12">
+        <v>0.6654009897232557</v>
+      </c>
+      <c r="M12">
+        <v>0.7749092401995692</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>4</v>
       </c>
       <c r="E13" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G13">
-        <v>10018.38219735946</v>
+        <v>2369.348836164419</v>
       </c>
       <c r="H13">
-        <v>9454.706519928746</v>
+        <v>2211.284760095633</v>
       </c>
       <c r="I13">
-        <v>-563.675677430716</v>
+        <v>-158.0640760687866</v>
       </c>
       <c r="J13">
-        <v>-0.05626414188702878</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
+        <v>-0.06671203229181986</v>
+      </c>
+      <c r="K13">
+        <v>0.1586287042417198</v>
+      </c>
+      <c r="L13">
+        <v>0.1556252502207414</v>
+      </c>
+      <c r="M13">
+        <v>0.2172974956939943</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>5</v>
       </c>
       <c r="E14" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F14" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G14">
         <v>2443.987754662811</v>
@@ -1918,89 +2323,116 @@
       <c r="J14">
         <v>-0.01431517488000416</v>
       </c>
-    </row>
-    <row r="15" spans="1:10">
+      <c r="K14">
+        <v>0.4082140634723086</v>
+      </c>
+      <c r="L14">
+        <v>0.4104836703607108</v>
+      </c>
+      <c r="M14">
+        <v>0.2956548262474083</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>5</v>
       </c>
       <c r="E15" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F15" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G15">
-        <v>771.1973555109769</v>
+        <v>2771.839770532215</v>
       </c>
       <c r="H15">
-        <v>741.4044825486761</v>
+        <v>2718.284437995423</v>
       </c>
       <c r="I15">
-        <v>-29.79287296230075</v>
+        <v>-53.55533253679232</v>
       </c>
       <c r="J15">
-        <v>-0.03863196981862146</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>-0.01932122235424498</v>
+      </c>
+      <c r="K15">
+        <v>0.4629744866210333</v>
+      </c>
+      <c r="L15">
+        <v>0.4631841479408621</v>
+      </c>
+      <c r="M15">
+        <v>0.4525765104974608</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>5</v>
       </c>
       <c r="E16" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F16" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G16">
-        <v>2771.839770532215</v>
+        <v>771.1973555109769</v>
       </c>
       <c r="H16">
-        <v>2718.284437995423</v>
+        <v>741.4044825486761</v>
       </c>
       <c r="I16">
-        <v>-53.55533253679232</v>
+        <v>-29.79287296230075</v>
       </c>
       <c r="J16">
-        <v>-0.01932122235424498</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
+        <v>-0.03863196981862146</v>
+      </c>
+      <c r="K16">
+        <v>0.1288114499066581</v>
+      </c>
+      <c r="L16">
+        <v>0.126332181698427</v>
+      </c>
+      <c r="M16">
+        <v>0.2517686632551309</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17">
         <v>6</v>
       </c>
       <c r="E17" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F17" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G17">
         <v>737.9275791029602</v>
@@ -2014,89 +2446,116 @@
       <c r="J17">
         <v>0.02527738081884549</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17">
+        <v>0.7150284321689699</v>
+      </c>
+      <c r="L17">
+        <v>0.7220370319238563</v>
+      </c>
+      <c r="M17">
+        <v>1.179358721779987</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D18">
         <v>6</v>
       </c>
       <c r="E18" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F18" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G18">
-        <v>76.96177205368217</v>
+        <v>217.1361542691039</v>
       </c>
       <c r="H18">
-        <v>75.15174688619692</v>
+        <v>216.1094207703017</v>
       </c>
       <c r="I18">
-        <v>-1.81002516748525</v>
+        <v>-1.026733498802173</v>
       </c>
       <c r="J18">
-        <v>-0.02351849651048479</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>-0.004728523917438958</v>
+      </c>
+      <c r="K18">
+        <v>0.2103980503655553</v>
+      </c>
+      <c r="L18">
+        <v>0.2062424473192178</v>
+      </c>
+      <c r="M18">
+        <v>-0.06491691032528364</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D19">
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F19" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G19">
-        <v>217.1361542691039</v>
+        <v>76.96177205368217</v>
       </c>
       <c r="H19">
-        <v>216.1094207703017</v>
+        <v>75.15174688619692</v>
       </c>
       <c r="I19">
-        <v>-1.026733498802173</v>
+        <v>-1.81002516748525</v>
       </c>
       <c r="J19">
-        <v>-0.004728523917438958</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>-0.02351849651048479</v>
+      </c>
+      <c r="K19">
+        <v>0.07457351746547462</v>
+      </c>
+      <c r="L19">
+        <v>0.07172052075692592</v>
+      </c>
+      <c r="M19">
+        <v>-0.1144418114547037</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F20" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G20">
         <v>28420.73848797222</v>
@@ -2110,89 +2569,116 @@
       <c r="J20">
         <v>0.03719956910429145</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20">
+        <v>0.1642038946162641</v>
+      </c>
+      <c r="L20">
+        <v>0.1684715681373224</v>
+      </c>
+      <c r="M20">
+        <v>0.5590864708306066</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D21">
         <v>7</v>
       </c>
       <c r="E21" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F21" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G21">
-        <v>19251.15945017174</v>
+        <v>125410.102061856</v>
       </c>
       <c r="H21">
-        <v>18859.45959321535</v>
+        <v>126635.5746934341</v>
       </c>
       <c r="I21">
-        <v>-391.6998569563912</v>
+        <v>1225.472631578057</v>
       </c>
       <c r="J21">
-        <v>-0.02034681900434297</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
+        <v>0.009771721826473095</v>
+      </c>
+      <c r="K21">
+        <v>0.7245704467353974</v>
+      </c>
+      <c r="L21">
+        <v>0.7237434690410091</v>
+      </c>
+      <c r="M21">
+        <v>0.6480512189124487</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D22">
         <v>7</v>
       </c>
       <c r="E22" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F22" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G22">
-        <v>125410.102061856</v>
+        <v>19251.15945017174</v>
       </c>
       <c r="H22">
-        <v>126635.5746934341</v>
+        <v>18859.45959321535</v>
       </c>
       <c r="I22">
-        <v>1225.472631578057</v>
+        <v>-391.6998569563912</v>
       </c>
       <c r="J22">
-        <v>0.009771721826473095</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>-0.02034681900434297</v>
+      </c>
+      <c r="K22">
+        <v>0.1112256586483386</v>
+      </c>
+      <c r="L22">
+        <v>0.1077849628216685</v>
+      </c>
+      <c r="M22">
+        <v>-0.2071376897430553</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D23">
         <v>8</v>
       </c>
       <c r="E23" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G23">
         <v>19646.96893063571</v>
@@ -2206,89 +2692,116 @@
       <c r="J23">
         <v>0.05442807630137755</v>
       </c>
-    </row>
-    <row r="24" spans="1:10">
+      <c r="K23">
+        <v>0.1703395953757214</v>
+      </c>
+      <c r="L23">
+        <v>0.1771289185151771</v>
+      </c>
+      <c r="M23">
+        <v>0.6616646788393241</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D24">
         <v>8</v>
       </c>
       <c r="E24" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F24" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G24">
-        <v>60774.34609826608</v>
+        <v>34918.68497109821</v>
       </c>
       <c r="H24">
-        <v>60014.07059865597</v>
+        <v>36225.75974666086</v>
       </c>
       <c r="I24">
-        <v>-760.2754996101139</v>
+        <v>1307.074775562643</v>
       </c>
       <c r="J24">
-        <v>-0.01250980962231702</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
+        <v>0.03743195875344372</v>
+      </c>
+      <c r="K24">
+        <v>0.3027456647398839</v>
+      </c>
+      <c r="L24">
+        <v>0.3097379743229643</v>
+      </c>
+      <c r="M24">
+        <v>0.8087603320261118</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D25">
         <v>8</v>
       </c>
       <c r="E25" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F25" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G25">
-        <v>34918.68497109821</v>
+        <v>60774.34609826608</v>
       </c>
       <c r="H25">
-        <v>36225.75974666086</v>
+        <v>60014.07059865597</v>
       </c>
       <c r="I25">
-        <v>1307.074775562643</v>
+        <v>-760.2754996101139</v>
       </c>
       <c r="J25">
-        <v>0.03743195875344372</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
+        <v>-0.01250980962231702</v>
+      </c>
+      <c r="K25">
+        <v>0.5269147398843946</v>
+      </c>
+      <c r="L25">
+        <v>0.5131331071618586</v>
+      </c>
+      <c r="M25">
+        <v>-0.4704250108654359</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D26">
         <v>9</v>
       </c>
       <c r="E26" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F26" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G26">
         <v>6147.44206383908</v>
@@ -2302,89 +2815,116 @@
       <c r="J26">
         <v>0.02481979087750858</v>
       </c>
-    </row>
-    <row r="27" spans="1:10">
+      <c r="K26">
+        <v>0.08832531700918218</v>
+      </c>
+      <c r="L26">
+        <v>0.08787128903718494</v>
+      </c>
+      <c r="M26">
+        <v>0.07279481644886465</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D27">
         <v>9</v>
       </c>
       <c r="E27" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F27" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G27">
-        <v>34734.06209007435</v>
+        <v>28718.49584608657</v>
       </c>
       <c r="H27">
-        <v>35597.97077432211</v>
+        <v>29798.01293538272</v>
       </c>
       <c r="I27">
-        <v>863.9086842477554</v>
+        <v>1079.517089296154</v>
       </c>
       <c r="J27">
-        <v>0.02487208901761672</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>0.03758961106743543</v>
+      </c>
+      <c r="K27">
+        <v>0.4126220667541173</v>
+      </c>
+      <c r="L27">
+        <v>0.415616091175496</v>
+      </c>
+      <c r="M27">
+        <v>0.5150357963516083</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D28">
         <v>9</v>
       </c>
       <c r="E28" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F28" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G28">
-        <v>28718.49584608657</v>
+        <v>34734.06209007435</v>
       </c>
       <c r="H28">
-        <v>29798.01293538272</v>
+        <v>35597.97077432211</v>
       </c>
       <c r="I28">
-        <v>1079.517089296154</v>
+        <v>863.9086842477554</v>
       </c>
       <c r="J28">
-        <v>0.03758961106743543</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
+        <v>0.02487208901761672</v>
+      </c>
+      <c r="K28">
+        <v>0.4990526162367004</v>
+      </c>
+      <c r="L28">
+        <v>0.4965126197873192</v>
+      </c>
+      <c r="M28">
+        <v>0.412169387199527</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D29">
         <v>10</v>
       </c>
       <c r="E29" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F29" t="s">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="G29">
         <v>3914.073253833027</v>
@@ -2398,69 +2938,96 @@
       <c r="J29">
         <v>-0.07983986820489161</v>
       </c>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="K29">
+        <v>0.08347529812606426</v>
+      </c>
+      <c r="L29">
+        <v>0.08631932144470537</v>
+      </c>
+      <c r="M29">
+        <v>0.06050142033165726</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D30">
         <v>10</v>
       </c>
       <c r="E30" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F30" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G30">
-        <v>10643.88287904598</v>
+        <v>32331.043867121</v>
       </c>
       <c r="H30">
-        <v>9488.084725005965</v>
+        <v>28634.18811389134</v>
       </c>
       <c r="I30">
-        <v>-1155.798154040016</v>
+        <v>-3696.855753229658</v>
       </c>
       <c r="J30">
-        <v>-0.1085880187873329</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>-0.1143438414306557</v>
+      </c>
+      <c r="K30">
+        <v>0.6895229982964234</v>
+      </c>
+      <c r="L30">
+        <v>0.6862787152366686</v>
+      </c>
+      <c r="M30">
+        <v>0.7157301542141465</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D31">
         <v>10</v>
       </c>
       <c r="E31" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F31" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="G31">
-        <v>32331.043867121</v>
+        <v>10643.88287904598</v>
       </c>
       <c r="H31">
-        <v>28634.18811389134</v>
+        <v>9488.084725005965</v>
       </c>
       <c r="I31">
-        <v>-3696.855753229658</v>
+        <v>-1155.798154040016</v>
       </c>
       <c r="J31">
-        <v>-0.1143438414306557</v>
+        <v>-0.1085880187873329</v>
+      </c>
+      <c r="K31">
+        <v>0.2270017035775125</v>
+      </c>
+      <c r="L31">
+        <v>0.227401963318626</v>
+      </c>
+      <c r="M31">
+        <v>0.2237684254541961</v>
       </c>
     </row>
   </sheetData>
@@ -2470,10 +3037,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J41"/>
+  <dimension ref="A1:M41"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:13">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2504,89 +3071,116 @@
       <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="2" spans="1:10">
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2">
         <v>1</v>
       </c>
       <c r="E2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F2" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G2">
-        <v>358.2232023220635</v>
+        <v>3451.96904055808</v>
       </c>
       <c r="H2">
-        <v>335.0327142331417</v>
+        <v>3302.062605575837</v>
       </c>
       <c r="I2">
-        <v>-23.19048808892177</v>
+        <v>-149.9064349822438</v>
       </c>
       <c r="J2">
-        <v>-0.06473753776583173</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+        <v>-0.04342635557299448</v>
+      </c>
+      <c r="K2">
+        <v>0.1624634248293149</v>
+      </c>
+      <c r="L2">
+        <v>0.1680227242756014</v>
+      </c>
+      <c r="M2">
+        <v>0.09397388447319024</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D3">
         <v>1</v>
       </c>
       <c r="E3" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G3">
-        <v>3451.96904055808</v>
+        <v>358.2232023220635</v>
       </c>
       <c r="H3">
-        <v>3302.062605575837</v>
+        <v>335.0327142331417</v>
       </c>
       <c r="I3">
-        <v>-149.9064349822438</v>
+        <v>-23.19048808892177</v>
       </c>
       <c r="J3">
-        <v>-0.04342635557299448</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>-0.06473753776583173</v>
+      </c>
+      <c r="K3">
+        <v>0.01685941201058921</v>
+      </c>
+      <c r="L3">
+        <v>0.01704786253048183</v>
+      </c>
+      <c r="M3">
+        <v>0.01453773648078125</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D4">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G4">
         <v>12813.14065826372</v>
@@ -2600,25 +3194,34 @@
       <c r="J4">
         <v>-0.08095433323636185</v>
       </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="K4">
+        <v>0.6030374808415785</v>
+      </c>
+      <c r="L4">
+        <v>0.5992049665301145</v>
+      </c>
+      <c r="M4">
+        <v>0.6502533479011925</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C5" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D5">
         <v>1</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G5">
         <v>4624.335884521229</v>
@@ -2632,89 +3235,116 @@
       <c r="J5">
         <v>-0.08321547572827036</v>
       </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="K5">
+        <v>0.2176396823185174</v>
+      </c>
+      <c r="L5">
+        <v>0.2157244466638025</v>
+      </c>
+      <c r="M5">
+        <v>0.241235031144836</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D6">
         <v>2</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G6">
-        <v>109.9026098247154</v>
+        <v>1664.428681321303</v>
       </c>
       <c r="H6">
-        <v>105.7805933466526</v>
+        <v>1677.026407533276</v>
       </c>
       <c r="I6">
-        <v>-4.122016478062832</v>
+        <v>12.5977262119734</v>
       </c>
       <c r="J6">
-        <v>-0.03750608365567543</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+        <v>0.00756879904398951</v>
+      </c>
+      <c r="K6">
+        <v>0.2665394402035619</v>
+      </c>
+      <c r="L6">
+        <v>0.2745862662578333</v>
+      </c>
+      <c r="M6">
+        <v>-0.09187346646117013</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D7">
         <v>2</v>
       </c>
       <c r="E7" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F7" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>1664.428681321303</v>
+        <v>109.9026098247154</v>
       </c>
       <c r="H7">
-        <v>1677.026407533276</v>
+        <v>105.7805933466526</v>
       </c>
       <c r="I7">
-        <v>12.5977262119734</v>
+        <v>-4.122016478062832</v>
       </c>
       <c r="J7">
-        <v>0.00756879904398951</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+        <v>-0.03750608365567543</v>
+      </c>
+      <c r="K7">
+        <v>0.01759966072943158</v>
+      </c>
+      <c r="L7">
+        <v>0.01731988121303284</v>
+      </c>
+      <c r="M7">
+        <v>0.03006129330622859</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B8" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D8">
         <v>2</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F8" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G8">
         <v>3583.089905851598</v>
@@ -2728,25 +3358,34 @@
       <c r="J8">
         <v>-0.03151553353281562</v>
       </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="K8">
+        <v>0.5737913486005096</v>
+      </c>
+      <c r="L8">
+        <v>0.5681843603733253</v>
+      </c>
+      <c r="M8">
+        <v>0.8235316728707623</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B9" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D9">
         <v>2</v>
       </c>
       <c r="E9" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G9">
         <v>887.16564557301</v>
@@ -2760,89 +3399,116 @@
       <c r="J9">
         <v>-0.03682865426945892</v>
       </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="K9">
+        <v>0.1420695504664969</v>
+      </c>
+      <c r="L9">
+        <v>0.1399094921558085</v>
+      </c>
+      <c r="M9">
+        <v>0.2382805002841791</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B10" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D10">
         <v>3</v>
       </c>
       <c r="E10" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F10" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G10">
-        <v>68.01361503497709</v>
+        <v>1144.895853088782</v>
       </c>
       <c r="H10">
-        <v>55.77432205469776</v>
+        <v>992.2301162322491</v>
       </c>
       <c r="I10">
-        <v>-12.23929298027934</v>
+        <v>-152.6657368565326</v>
       </c>
       <c r="J10">
-        <v>-0.1799535721485336</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
+        <v>-0.1333446500349006</v>
+      </c>
+      <c r="K10">
+        <v>0.1268844221105523</v>
+      </c>
+      <c r="L10">
+        <v>0.1328344022444252</v>
+      </c>
+      <c r="M10">
+        <v>0.09827450286914927</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D11">
         <v>3</v>
       </c>
       <c r="E11" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F11" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G11">
-        <v>1144.895853088782</v>
+        <v>68.01361503497709</v>
       </c>
       <c r="H11">
-        <v>992.2301162322491</v>
+        <v>55.77432205469776</v>
       </c>
       <c r="I11">
-        <v>-152.6657368565326</v>
+        <v>-12.23929298027934</v>
       </c>
       <c r="J11">
-        <v>-0.1333446500349006</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
+        <v>-0.1799535721485336</v>
+      </c>
+      <c r="K11">
+        <v>0.007537688442211023</v>
+      </c>
+      <c r="L11">
+        <v>0.007466764623973264</v>
+      </c>
+      <c r="M11">
+        <v>0.007878718944232782</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D12">
         <v>3</v>
       </c>
       <c r="E12" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F12" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G12">
         <v>6183.571166930033</v>
@@ -2856,25 +3522,34 @@
       <c r="J12">
         <v>-0.1813075822358861</v>
       </c>
-    </row>
-    <row r="13" spans="1:10">
+      <c r="K12">
+        <v>0.685301507537689</v>
+      </c>
+      <c r="L12">
+        <v>0.6777324696106505</v>
+      </c>
+      <c r="M12">
+        <v>0.7216965137318911</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D13">
         <v>3</v>
       </c>
       <c r="E13" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G13">
         <v>1626.658959586543</v>
@@ -2888,89 +3563,116 @@
       <c r="J13">
         <v>-0.1644038210890883</v>
       </c>
-    </row>
-    <row r="14" spans="1:10">
+      <c r="K13">
+        <v>0.1802763819095477</v>
+      </c>
+      <c r="L13">
+        <v>0.181966363520951</v>
+      </c>
+      <c r="M13">
+        <v>0.1721502644547268</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D14">
         <v>4</v>
       </c>
       <c r="E14" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F14" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G14">
-        <v>257.4750261521749</v>
+        <v>2548.713461124355</v>
       </c>
       <c r="H14">
-        <v>251.5820998087408</v>
+        <v>2543.044573470543</v>
       </c>
       <c r="I14">
-        <v>-5.892926343434084</v>
+        <v>-5.668887653811908</v>
       </c>
       <c r="J14">
-        <v>-0.02288737059861954</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
+        <v>-0.00222421536994241</v>
+      </c>
+      <c r="K14">
+        <v>0.1706372264187481</v>
+      </c>
+      <c r="L14">
+        <v>0.1789737600560029</v>
+      </c>
+      <c r="M14">
+        <v>0.00779326410643653</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D15">
         <v>4</v>
       </c>
       <c r="E15" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F15" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G15">
-        <v>2548.713461124355</v>
+        <v>257.4750261521749</v>
       </c>
       <c r="H15">
-        <v>2543.044573470543</v>
+        <v>251.5820998087408</v>
       </c>
       <c r="I15">
-        <v>-5.668887653811908</v>
+        <v>-5.892926343434084</v>
       </c>
       <c r="J15">
-        <v>-0.00222421536994241</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
+        <v>-0.02288737059861954</v>
+      </c>
+      <c r="K15">
+        <v>0.01723803989928318</v>
+      </c>
+      <c r="L15">
+        <v>0.01770578260219257</v>
+      </c>
+      <c r="M15">
+        <v>0.008101259745953486</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B16" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D16">
         <v>4</v>
       </c>
       <c r="E16" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F16" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G16">
         <v>9677.010814371186</v>
@@ -2984,25 +3686,34 @@
       <c r="J16">
         <v>-0.05677590087411744</v>
       </c>
-    </row>
-    <row r="17" spans="1:10">
+      <c r="K16">
+        <v>0.6478791400348646</v>
+      </c>
+      <c r="L16">
+        <v>0.6423792509026304</v>
+      </c>
+      <c r="M16">
+        <v>0.7553127302466282</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D17">
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="F17" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G17">
         <v>2453.245193000522</v>
@@ -3016,89 +3727,116 @@
       <c r="J17">
         <v>-0.06783904881436519</v>
       </c>
-    </row>
-    <row r="18" spans="1:10">
+      <c r="K17">
+        <v>0.1642455936471043</v>
+      </c>
+      <c r="L17">
+        <v>0.1609412064391741</v>
+      </c>
+      <c r="M17">
+        <v>0.2287927459009819</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B18" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C18" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D18">
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F18" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G18">
-        <v>197.4563277395255</v>
+        <v>2443.987754662811</v>
       </c>
       <c r="H18">
-        <v>186.0946485799231</v>
+        <v>2409.001642550224</v>
       </c>
       <c r="I18">
-        <v>-11.36167915960237</v>
+        <v>-34.98611211258685</v>
       </c>
       <c r="J18">
-        <v>-0.05754021301657211</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
+        <v>-0.01431517488000416</v>
+      </c>
+      <c r="K18">
+        <v>0.4082140634723086</v>
+      </c>
+      <c r="L18">
+        <v>0.4104836703607108</v>
+      </c>
+      <c r="M18">
+        <v>0.2956548262474084</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C19" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D19">
         <v>5</v>
       </c>
       <c r="E19" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F19" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G19">
-        <v>2443.987754662811</v>
+        <v>197.4563277395255</v>
       </c>
       <c r="H19">
-        <v>2409.001642550224</v>
+        <v>186.0946485799231</v>
       </c>
       <c r="I19">
-        <v>-34.98611211258685</v>
+        <v>-11.36167915960237</v>
       </c>
       <c r="J19">
-        <v>-0.01431517488000416</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
+        <v>-0.05754021301657211</v>
+      </c>
+      <c r="K19">
+        <v>0.03298070939639072</v>
+      </c>
+      <c r="L19">
+        <v>0.03170973943492481</v>
+      </c>
+      <c r="M19">
+        <v>0.0960133914566213</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B20" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D20">
         <v>5</v>
       </c>
       <c r="E20" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F20" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G20">
         <v>2563.206669524415</v>
@@ -3112,25 +3850,34 @@
       <c r="J20">
         <v>-0.01574273645324365</v>
       </c>
-    </row>
-    <row r="21" spans="1:10">
+      <c r="K20">
+        <v>0.4281269446172998</v>
+      </c>
+      <c r="L20">
+        <v>0.4298837628816293</v>
+      </c>
+      <c r="M20">
+        <v>0.3409990262160133</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B21" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C21" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D21">
         <v>5</v>
       </c>
       <c r="E21" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F21" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G21">
         <v>782.3741287792515</v>
@@ -3144,89 +3891,116 @@
       <c r="J21">
         <v>-0.04043415816334739</v>
       </c>
-    </row>
-    <row r="22" spans="1:10">
+      <c r="K21">
+        <v>0.1306782825140009</v>
+      </c>
+      <c r="L21">
+        <v>0.1279228273227351</v>
+      </c>
+      <c r="M21">
+        <v>0.267332756079957</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B22" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C22" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D22">
         <v>6</v>
       </c>
       <c r="E22" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F22" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G22">
-        <v>75.03353593469043</v>
+        <v>737.9275791029602</v>
       </c>
       <c r="H22">
-        <v>75.0420923253308</v>
+        <v>756.5804555366744</v>
       </c>
       <c r="I22">
-        <v>0.008556390640364953</v>
+        <v>18.65287643371425</v>
       </c>
       <c r="J22">
-        <v>0.0001140342186167593</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
+        <v>0.02527738081884549</v>
+      </c>
+      <c r="K22">
+        <v>0.7150284321689699</v>
+      </c>
+      <c r="L22">
+        <v>0.7220370319238563</v>
+      </c>
+      <c r="M22">
+        <v>1.179358721779986</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B23" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D23">
         <v>6</v>
       </c>
       <c r="E23" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F23" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G23">
-        <v>737.9275791029602</v>
+        <v>75.03353593469043</v>
       </c>
       <c r="H23">
-        <v>756.5804555366744</v>
+        <v>75.0420923253308</v>
       </c>
       <c r="I23">
-        <v>18.65287643371425</v>
+        <v>0.008556390640364953</v>
       </c>
       <c r="J23">
-        <v>0.02527738081884549</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
+        <v>0.0001140342186167593</v>
+      </c>
+      <c r="K23">
+        <v>0.072705117790414</v>
+      </c>
+      <c r="L23">
+        <v>0.07161587272764458</v>
+      </c>
+      <c r="M23">
+        <v>0.0005409918392228188</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B24" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D24">
         <v>6</v>
       </c>
       <c r="E24" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F24" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G24">
         <v>137.9108006844309</v>
@@ -3240,25 +4014,34 @@
       <c r="J24">
         <v>-0.008805413455624241</v>
       </c>
-    </row>
-    <row r="25" spans="1:10">
+      <c r="K24">
+        <v>0.133631194151096</v>
+      </c>
+      <c r="L24">
+        <v>0.1304552482347877</v>
+      </c>
+      <c r="M24">
+        <v>-0.0767800061860672</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B25" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C25" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D25">
         <v>6</v>
       </c>
       <c r="E25" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="F25" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G25">
         <v>81.15358970366472</v>
@@ -3272,89 +4055,116 @@
       <c r="J25">
         <v>-0.02009712007639661</v>
       </c>
-    </row>
-    <row r="26" spans="1:10">
+      <c r="K25">
+        <v>0.07863525588951994</v>
+      </c>
+      <c r="L25">
+        <v>0.07589184711371147</v>
+      </c>
+      <c r="M25">
+        <v>-0.1031197074331419</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B26" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C26" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D26">
         <v>7</v>
       </c>
       <c r="E26" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F26" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G26">
-        <v>2795.482474226756</v>
+        <v>28420.73848797222</v>
       </c>
       <c r="H26">
-        <v>2720.328558298284</v>
+        <v>29477.97771335054</v>
       </c>
       <c r="I26">
-        <v>-75.15391592847118</v>
+        <v>1057.239225378318</v>
       </c>
       <c r="J26">
-        <v>-0.02688405905648152</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
+        <v>0.03719956910429145</v>
+      </c>
+      <c r="K26">
+        <v>0.1642038946162641</v>
+      </c>
+      <c r="L26">
+        <v>0.1684715681373224</v>
+      </c>
+      <c r="M26">
+        <v>0.5590864708306125</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B27" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C27" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D27">
         <v>7</v>
       </c>
       <c r="E27" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F27" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G27">
-        <v>28420.73848797222</v>
+        <v>2795.482474226756</v>
       </c>
       <c r="H27">
-        <v>29477.97771335054</v>
+        <v>2720.328558298284</v>
       </c>
       <c r="I27">
-        <v>1057.239225378318</v>
+        <v>-75.15391592847118</v>
       </c>
       <c r="J27">
-        <v>0.03719956910429145</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
+        <v>-0.02688405905648152</v>
+      </c>
+      <c r="K27">
+        <v>0.01615120274914061</v>
+      </c>
+      <c r="L27">
+        <v>0.01554713225316305</v>
+      </c>
+      <c r="M27">
+        <v>-0.03974269646542306</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B28" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C28" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D28">
         <v>7</v>
       </c>
       <c r="E28" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F28" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G28">
         <v>122029.7491408939</v>
@@ -3368,25 +4178,34 @@
       <c r="J28">
         <v>0.01052237457105928</v>
       </c>
-    </row>
-    <row r="29" spans="1:10">
+      <c r="K28">
+        <v>0.7050400916380323</v>
+      </c>
+      <c r="L28">
+        <v>0.7047589251659383</v>
+      </c>
+      <c r="M28">
+        <v>0.6790241041690427</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B29" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C29" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D29">
         <v>7</v>
       </c>
       <c r="E29" t="s">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="F29" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G29">
         <v>19836.02989690712</v>
@@ -3400,89 +4219,116 @@
       <c r="J29">
         <v>-0.01891084257648035</v>
       </c>
-    </row>
-    <row r="30" spans="1:10">
+      <c r="K29">
+        <v>0.114604810996563</v>
+      </c>
+      <c r="L29">
+        <v>0.1112223744435762</v>
+      </c>
+      <c r="M29">
+        <v>-0.1983678785342321</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B30" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C30" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D30">
         <v>8</v>
       </c>
       <c r="E30" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F30" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G30">
-        <v>822.964234104015</v>
+        <v>19646.96893063571</v>
       </c>
       <c r="H30">
-        <v>879.2572806078971</v>
+        <v>20716.31565468315</v>
       </c>
       <c r="I30">
-        <v>56.29304650388212</v>
+        <v>1069.346724047435</v>
       </c>
       <c r="J30">
-        <v>0.06840278613707922</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
+        <v>0.05442807630137755</v>
+      </c>
+      <c r="K30">
+        <v>0.1703395953757214</v>
+      </c>
+      <c r="L30">
+        <v>0.1771289185151771</v>
+      </c>
+      <c r="M30">
+        <v>0.6616646788393236</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B31" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C31" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D31">
         <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F31" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G31">
-        <v>19646.96893063571</v>
+        <v>822.964234104015</v>
       </c>
       <c r="H31">
-        <v>20716.31565468315</v>
+        <v>879.2572806078971</v>
       </c>
       <c r="I31">
-        <v>1069.346724047435</v>
+        <v>56.29304650388212</v>
       </c>
       <c r="J31">
-        <v>0.05442807630137755</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
+        <v>0.06840278613707922</v>
+      </c>
+      <c r="K31">
+        <v>0.007135115606936144</v>
+      </c>
+      <c r="L31">
+        <v>0.007517837332019279</v>
+      </c>
+      <c r="M31">
+        <v>0.03483165908518372</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B32" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C32" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D32">
         <v>8</v>
       </c>
       <c r="E32" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F32" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G32">
         <v>29126.68352601153</v>
@@ -3496,25 +4342,34 @@
       <c r="J32">
         <v>0.03735969350004975</v>
       </c>
-    </row>
-    <row r="33" spans="1:10">
+      <c r="K32">
+        <v>0.2525289017341038</v>
+      </c>
+      <c r="L32">
+        <v>0.2583433921909181</v>
+      </c>
+      <c r="M32">
+        <v>0.6733079617836275</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B33" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C33" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D33">
         <v>8</v>
       </c>
       <c r="E33" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="F33" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G33">
         <v>65743.38330924875</v>
@@ -3528,89 +4383,116 @@
       <c r="J33">
         <v>-0.009090766396137271</v>
       </c>
-    </row>
-    <row r="34" spans="1:10">
+      <c r="K33">
+        <v>0.5699963872832385</v>
+      </c>
+      <c r="L33">
+        <v>0.5570098519618856</v>
+      </c>
+      <c r="M33">
+        <v>-0.3698042997081348</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B34" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D34">
         <v>9</v>
       </c>
       <c r="E34" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F34" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G34">
-        <v>50.72146917358625</v>
+        <v>6147.44206383908</v>
       </c>
       <c r="H34">
-        <v>51.50919573397206</v>
+        <v>6300.020290295166</v>
       </c>
       <c r="I34">
-        <v>0.7877265603858064</v>
+        <v>152.5782264560858</v>
       </c>
       <c r="J34">
-        <v>0.01553043658277989</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
+        <v>0.02481979087750858</v>
+      </c>
+      <c r="K34">
+        <v>0.08832531700918218</v>
+      </c>
+      <c r="L34">
+        <v>0.08787128903718494</v>
+      </c>
+      <c r="M34">
+        <v>0.07279481644886471</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B35" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C35" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D35">
         <v>9</v>
       </c>
       <c r="E35" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F35" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G35">
-        <v>6147.44206383908</v>
+        <v>50.72146917358625</v>
       </c>
       <c r="H35">
-        <v>6300.020290295166</v>
+        <v>51.50919573397206</v>
       </c>
       <c r="I35">
-        <v>152.5782264560858</v>
+        <v>0.7877265603858064</v>
       </c>
       <c r="J35">
-        <v>0.02481979087750858</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
+        <v>0.01553043658277989</v>
+      </c>
+      <c r="K35">
+        <v>0.0007287567409998024</v>
+      </c>
+      <c r="L35">
+        <v>0.0007184388649327244</v>
+      </c>
+      <c r="M35">
+        <v>0.000375823023422574</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B36" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C36" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D36">
         <v>9</v>
       </c>
       <c r="E36" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F36" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G36">
         <v>12365.89418452115</v>
@@ -3624,25 +4506,34 @@
       <c r="J36">
         <v>0.02147291423728611</v>
       </c>
-    </row>
-    <row r="37" spans="1:10">
+      <c r="K36">
+        <v>0.1776708934557636</v>
+      </c>
+      <c r="L36">
+        <v>0.1761803345387664</v>
+      </c>
+      <c r="M36">
+        <v>0.126684770301764</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B37" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C37" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D37">
         <v>9</v>
       </c>
       <c r="E37" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="F37" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G37">
         <v>51035.94228246618</v>
@@ -3656,89 +4547,116 @@
       <c r="J37">
         <v>0.03286127749752801</v>
       </c>
-    </row>
-    <row r="38" spans="1:10">
+      <c r="K37">
+        <v>0.7332750327940544</v>
+      </c>
+      <c r="L37">
+        <v>0.735229937559116</v>
+      </c>
+      <c r="M37">
+        <v>0.8001445902259487</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B38" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C38" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D38">
         <v>10</v>
       </c>
       <c r="E38" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F38" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G38">
-        <v>129.8034497444613</v>
+        <v>3914.073253833027</v>
       </c>
       <c r="H38">
-        <v>104.1471664191177</v>
+        <v>3601.574161102707</v>
       </c>
       <c r="I38">
-        <v>-25.65628332534352</v>
+        <v>-312.4990927303202</v>
       </c>
       <c r="J38">
-        <v>-0.1976548649196304</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
+        <v>-0.07983986820489161</v>
+      </c>
+      <c r="K38">
+        <v>0.08347529812606425</v>
+      </c>
+      <c r="L38">
+        <v>0.08631932144470537</v>
+      </c>
+      <c r="M38">
+        <v>0.06050142033165718</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B39" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C39" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D39">
         <v>10</v>
       </c>
       <c r="E39" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F39" t="s">
-        <v>23</v>
+        <v>31</v>
       </c>
       <c r="G39">
-        <v>3914.073253833027</v>
+        <v>129.8034497444613</v>
       </c>
       <c r="H39">
-        <v>3601.574161102707</v>
+        <v>104.1471664191177</v>
       </c>
       <c r="I39">
-        <v>-312.4990927303202</v>
+        <v>-25.65628332534352</v>
       </c>
       <c r="J39">
-        <v>-0.07983986820489161</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
+        <v>-0.1976548649196304</v>
+      </c>
+      <c r="K39">
+        <v>0.002768313458262305</v>
+      </c>
+      <c r="L39">
+        <v>0.002496106517194297</v>
+      </c>
+      <c r="M39">
+        <v>0.004967187482218536</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B40" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C40" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D40">
         <v>10</v>
       </c>
       <c r="E40" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F40" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G40">
         <v>5821.185477001693</v>
@@ -3752,25 +4670,34 @@
       <c r="J40">
         <v>-0.1302839422527272</v>
       </c>
-    </row>
-    <row r="41" spans="1:10">
+      <c r="K40">
+        <v>0.1241482112436113</v>
+      </c>
+      <c r="L40">
+        <v>0.1213401651212456</v>
+      </c>
+      <c r="M40">
+        <v>0.1468314670500763</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41" t="s">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="B41" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C41" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D41">
         <v>10</v>
       </c>
       <c r="E41" t="s">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="F41" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G41">
         <v>37023.93781942083</v>
@@ -3783,6 +4710,15 @@
       </c>
       <c r="J41">
         <v>-0.1098908131074611</v>
+      </c>
+      <c r="K41">
+        <v>0.7896081771720621</v>
+      </c>
+      <c r="L41">
+        <v>0.7898444069168546</v>
+      </c>
+      <c r="M41">
+        <v>0.787699925136048</v>
       </c>
     </row>
   </sheetData>
